--- a/04_Structural_QC/data/structural_wells_100_nonlinear.xlsx
+++ b/04_Structural_QC/data/structural_wells_100_nonlinear.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\My_project\ML_Geophysics\structural_qc_project\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5DC69A-EFFD-44C5-9DAA-32785EB70F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="wells" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -31,371 +37,371 @@
     <t>Z_map</t>
   </si>
   <si>
+    <t>well_category</t>
+  </si>
+  <si>
+    <t>reservoir_flag</t>
+  </si>
+  <si>
+    <t>fluid_type</t>
+  </si>
+  <si>
+    <t>T_well</t>
+  </si>
+  <si>
+    <t>T_map</t>
+  </si>
+  <si>
+    <t>W-001</t>
+  </si>
+  <si>
+    <t>W-002</t>
+  </si>
+  <si>
+    <t>W-003</t>
+  </si>
+  <si>
+    <t>W-004</t>
+  </si>
+  <si>
+    <t>W-005</t>
+  </si>
+  <si>
+    <t>W-006</t>
+  </si>
+  <si>
+    <t>W-007</t>
+  </si>
+  <si>
+    <t>W-008</t>
+  </si>
+  <si>
+    <t>W-009</t>
+  </si>
+  <si>
+    <t>W-010</t>
+  </si>
+  <si>
+    <t>W-011</t>
+  </si>
+  <si>
+    <t>W-012</t>
+  </si>
+  <si>
+    <t>W-013</t>
+  </si>
+  <si>
+    <t>W-014</t>
+  </si>
+  <si>
+    <t>W-015</t>
+  </si>
+  <si>
+    <t>W-016</t>
+  </si>
+  <si>
+    <t>W-017</t>
+  </si>
+  <si>
+    <t>W-018</t>
+  </si>
+  <si>
+    <t>W-019</t>
+  </si>
+  <si>
+    <t>W-020</t>
+  </si>
+  <si>
+    <t>W-021</t>
+  </si>
+  <si>
+    <t>W-022</t>
+  </si>
+  <si>
+    <t>W-023</t>
+  </si>
+  <si>
+    <t>W-024</t>
+  </si>
+  <si>
+    <t>W-025</t>
+  </si>
+  <si>
+    <t>W-026</t>
+  </si>
+  <si>
+    <t>W-027</t>
+  </si>
+  <si>
+    <t>W-028</t>
+  </si>
+  <si>
+    <t>W-029</t>
+  </si>
+  <si>
+    <t>W-030</t>
+  </si>
+  <si>
+    <t>W-031</t>
+  </si>
+  <si>
+    <t>W-032</t>
+  </si>
+  <si>
+    <t>W-033</t>
+  </si>
+  <si>
+    <t>W-034</t>
+  </si>
+  <si>
+    <t>W-035</t>
+  </si>
+  <si>
+    <t>W-036</t>
+  </si>
+  <si>
+    <t>W-037</t>
+  </si>
+  <si>
+    <t>W-038</t>
+  </si>
+  <si>
+    <t>W-039</t>
+  </si>
+  <si>
+    <t>W-040</t>
+  </si>
+  <si>
+    <t>W-041</t>
+  </si>
+  <si>
+    <t>W-042</t>
+  </si>
+  <si>
+    <t>W-043</t>
+  </si>
+  <si>
+    <t>W-044</t>
+  </si>
+  <si>
+    <t>W-045</t>
+  </si>
+  <si>
+    <t>W-046</t>
+  </si>
+  <si>
+    <t>W-047</t>
+  </si>
+  <si>
+    <t>W-048</t>
+  </si>
+  <si>
+    <t>W-049</t>
+  </si>
+  <si>
+    <t>W-050</t>
+  </si>
+  <si>
+    <t>W-051</t>
+  </si>
+  <si>
+    <t>W-052</t>
+  </si>
+  <si>
+    <t>W-053</t>
+  </si>
+  <si>
+    <t>W-054</t>
+  </si>
+  <si>
+    <t>W-055</t>
+  </si>
+  <si>
+    <t>W-056</t>
+  </si>
+  <si>
+    <t>W-057</t>
+  </si>
+  <si>
+    <t>W-058</t>
+  </si>
+  <si>
+    <t>W-059</t>
+  </si>
+  <si>
+    <t>W-060</t>
+  </si>
+  <si>
+    <t>W-061</t>
+  </si>
+  <si>
+    <t>W-062</t>
+  </si>
+  <si>
+    <t>W-063</t>
+  </si>
+  <si>
+    <t>W-064</t>
+  </si>
+  <si>
+    <t>W-065</t>
+  </si>
+  <si>
+    <t>W-066</t>
+  </si>
+  <si>
+    <t>W-067</t>
+  </si>
+  <si>
+    <t>W-068</t>
+  </si>
+  <si>
+    <t>W-069</t>
+  </si>
+  <si>
+    <t>W-070</t>
+  </si>
+  <si>
+    <t>W-071</t>
+  </si>
+  <si>
+    <t>W-072</t>
+  </si>
+  <si>
+    <t>W-073</t>
+  </si>
+  <si>
+    <t>W-074</t>
+  </si>
+  <si>
+    <t>W-075</t>
+  </si>
+  <si>
+    <t>W-076</t>
+  </si>
+  <si>
+    <t>W-077</t>
+  </si>
+  <si>
+    <t>W-078</t>
+  </si>
+  <si>
+    <t>W-079</t>
+  </si>
+  <si>
+    <t>W-080</t>
+  </si>
+  <si>
+    <t>W-081</t>
+  </si>
+  <si>
+    <t>W-082</t>
+  </si>
+  <si>
+    <t>W-083</t>
+  </si>
+  <si>
+    <t>W-084</t>
+  </si>
+  <si>
+    <t>W-085</t>
+  </si>
+  <si>
+    <t>W-086</t>
+  </si>
+  <si>
+    <t>W-087</t>
+  </si>
+  <si>
+    <t>W-088</t>
+  </si>
+  <si>
+    <t>W-089</t>
+  </si>
+  <si>
+    <t>W-090</t>
+  </si>
+  <si>
+    <t>W-091</t>
+  </si>
+  <si>
+    <t>W-092</t>
+  </si>
+  <si>
+    <t>W-093</t>
+  </si>
+  <si>
+    <t>W-094</t>
+  </si>
+  <si>
+    <t>W-095</t>
+  </si>
+  <si>
+    <t>W-096</t>
+  </si>
+  <si>
+    <t>W-097</t>
+  </si>
+  <si>
+    <t>W-098</t>
+  </si>
+  <si>
+    <t>W-099</t>
+  </si>
+  <si>
+    <t>W-100</t>
+  </si>
+  <si>
+    <t>Top_Reservoir</t>
+  </si>
+  <si>
+    <t>Top_Seal</t>
+  </si>
+  <si>
+    <t>Central_Graben</t>
+  </si>
+  <si>
+    <t>South_Block</t>
+  </si>
+  <si>
+    <t>North_Block</t>
+  </si>
+  <si>
+    <t>production</t>
+  </si>
+  <si>
+    <t>exploration</t>
+  </si>
+  <si>
+    <t>appraisal</t>
+  </si>
+  <si>
+    <t>non_reservoir</t>
+  </si>
+  <si>
+    <t>reservoir</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>gas</t>
+  </si>
+  <si>
+    <t>oil</t>
+  </si>
+  <si>
     <t>horizon_id</t>
   </si>
   <si>
     <t>tectonic_zone</t>
-  </si>
-  <si>
-    <t>well_category</t>
-  </si>
-  <si>
-    <t>reservoir_flag</t>
-  </si>
-  <si>
-    <t>fluid_type</t>
-  </si>
-  <si>
-    <t>T_well</t>
-  </si>
-  <si>
-    <t>T_map</t>
-  </si>
-  <si>
-    <t>W-001</t>
-  </si>
-  <si>
-    <t>W-002</t>
-  </si>
-  <si>
-    <t>W-003</t>
-  </si>
-  <si>
-    <t>W-004</t>
-  </si>
-  <si>
-    <t>W-005</t>
-  </si>
-  <si>
-    <t>W-006</t>
-  </si>
-  <si>
-    <t>W-007</t>
-  </si>
-  <si>
-    <t>W-008</t>
-  </si>
-  <si>
-    <t>W-009</t>
-  </si>
-  <si>
-    <t>W-010</t>
-  </si>
-  <si>
-    <t>W-011</t>
-  </si>
-  <si>
-    <t>W-012</t>
-  </si>
-  <si>
-    <t>W-013</t>
-  </si>
-  <si>
-    <t>W-014</t>
-  </si>
-  <si>
-    <t>W-015</t>
-  </si>
-  <si>
-    <t>W-016</t>
-  </si>
-  <si>
-    <t>W-017</t>
-  </si>
-  <si>
-    <t>W-018</t>
-  </si>
-  <si>
-    <t>W-019</t>
-  </si>
-  <si>
-    <t>W-020</t>
-  </si>
-  <si>
-    <t>W-021</t>
-  </si>
-  <si>
-    <t>W-022</t>
-  </si>
-  <si>
-    <t>W-023</t>
-  </si>
-  <si>
-    <t>W-024</t>
-  </si>
-  <si>
-    <t>W-025</t>
-  </si>
-  <si>
-    <t>W-026</t>
-  </si>
-  <si>
-    <t>W-027</t>
-  </si>
-  <si>
-    <t>W-028</t>
-  </si>
-  <si>
-    <t>W-029</t>
-  </si>
-  <si>
-    <t>W-030</t>
-  </si>
-  <si>
-    <t>W-031</t>
-  </si>
-  <si>
-    <t>W-032</t>
-  </si>
-  <si>
-    <t>W-033</t>
-  </si>
-  <si>
-    <t>W-034</t>
-  </si>
-  <si>
-    <t>W-035</t>
-  </si>
-  <si>
-    <t>W-036</t>
-  </si>
-  <si>
-    <t>W-037</t>
-  </si>
-  <si>
-    <t>W-038</t>
-  </si>
-  <si>
-    <t>W-039</t>
-  </si>
-  <si>
-    <t>W-040</t>
-  </si>
-  <si>
-    <t>W-041</t>
-  </si>
-  <si>
-    <t>W-042</t>
-  </si>
-  <si>
-    <t>W-043</t>
-  </si>
-  <si>
-    <t>W-044</t>
-  </si>
-  <si>
-    <t>W-045</t>
-  </si>
-  <si>
-    <t>W-046</t>
-  </si>
-  <si>
-    <t>W-047</t>
-  </si>
-  <si>
-    <t>W-048</t>
-  </si>
-  <si>
-    <t>W-049</t>
-  </si>
-  <si>
-    <t>W-050</t>
-  </si>
-  <si>
-    <t>W-051</t>
-  </si>
-  <si>
-    <t>W-052</t>
-  </si>
-  <si>
-    <t>W-053</t>
-  </si>
-  <si>
-    <t>W-054</t>
-  </si>
-  <si>
-    <t>W-055</t>
-  </si>
-  <si>
-    <t>W-056</t>
-  </si>
-  <si>
-    <t>W-057</t>
-  </si>
-  <si>
-    <t>W-058</t>
-  </si>
-  <si>
-    <t>W-059</t>
-  </si>
-  <si>
-    <t>W-060</t>
-  </si>
-  <si>
-    <t>W-061</t>
-  </si>
-  <si>
-    <t>W-062</t>
-  </si>
-  <si>
-    <t>W-063</t>
-  </si>
-  <si>
-    <t>W-064</t>
-  </si>
-  <si>
-    <t>W-065</t>
-  </si>
-  <si>
-    <t>W-066</t>
-  </si>
-  <si>
-    <t>W-067</t>
-  </si>
-  <si>
-    <t>W-068</t>
-  </si>
-  <si>
-    <t>W-069</t>
-  </si>
-  <si>
-    <t>W-070</t>
-  </si>
-  <si>
-    <t>W-071</t>
-  </si>
-  <si>
-    <t>W-072</t>
-  </si>
-  <si>
-    <t>W-073</t>
-  </si>
-  <si>
-    <t>W-074</t>
-  </si>
-  <si>
-    <t>W-075</t>
-  </si>
-  <si>
-    <t>W-076</t>
-  </si>
-  <si>
-    <t>W-077</t>
-  </si>
-  <si>
-    <t>W-078</t>
-  </si>
-  <si>
-    <t>W-079</t>
-  </si>
-  <si>
-    <t>W-080</t>
-  </si>
-  <si>
-    <t>W-081</t>
-  </si>
-  <si>
-    <t>W-082</t>
-  </si>
-  <si>
-    <t>W-083</t>
-  </si>
-  <si>
-    <t>W-084</t>
-  </si>
-  <si>
-    <t>W-085</t>
-  </si>
-  <si>
-    <t>W-086</t>
-  </si>
-  <si>
-    <t>W-087</t>
-  </si>
-  <si>
-    <t>W-088</t>
-  </si>
-  <si>
-    <t>W-089</t>
-  </si>
-  <si>
-    <t>W-090</t>
-  </si>
-  <si>
-    <t>W-091</t>
-  </si>
-  <si>
-    <t>W-092</t>
-  </si>
-  <si>
-    <t>W-093</t>
-  </si>
-  <si>
-    <t>W-094</t>
-  </si>
-  <si>
-    <t>W-095</t>
-  </si>
-  <si>
-    <t>W-096</t>
-  </si>
-  <si>
-    <t>W-097</t>
-  </si>
-  <si>
-    <t>W-098</t>
-  </si>
-  <si>
-    <t>W-099</t>
-  </si>
-  <si>
-    <t>W-100</t>
-  </si>
-  <si>
-    <t>Top_Reservoir</t>
-  </si>
-  <si>
-    <t>Top_Seal</t>
-  </si>
-  <si>
-    <t>Central_Graben</t>
-  </si>
-  <si>
-    <t>South_Block</t>
-  </si>
-  <si>
-    <t>North_Block</t>
-  </si>
-  <si>
-    <t>production</t>
-  </si>
-  <si>
-    <t>exploration</t>
-  </si>
-  <si>
-    <t>appraisal</t>
-  </si>
-  <si>
-    <t>non_reservoir</t>
-  </si>
-  <si>
-    <t>reservoir</t>
-  </si>
-  <si>
-    <t>water</t>
-  </si>
-  <si>
-    <t>gas</t>
-  </si>
-  <si>
-    <t>oil</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -428,17 +434,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -476,7 +490,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -510,6 +524,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -544,9 +559,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -719,11 +735,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L101"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -740,30 +756,30 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
-        <v>12</v>
       </c>
       <c r="B2">
         <v>7501.1</v>
@@ -772,25 +788,25 @@
         <v>9671.5</v>
       </c>
       <c r="D2">
-        <v>2319.03</v>
+        <v>2319.0300000000002</v>
       </c>
       <c r="E2">
         <v>2324.56</v>
       </c>
       <c r="F2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G2" t="s">
         <v>112</v>
       </c>
-      <c r="G2" t="s">
-        <v>114</v>
-      </c>
       <c r="H2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K2">
         <v>1713.24</v>
@@ -799,9 +815,9 @@
         <v>1807.63</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>10766.6</v>
@@ -810,25 +826,25 @@
         <v>6577.6</v>
       </c>
       <c r="D3">
-        <v>2485.68</v>
+        <v>2485.6799999999998</v>
       </c>
       <c r="E3">
-        <v>2427.74</v>
+        <v>2427.7399999999998</v>
       </c>
       <c r="F3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K3">
         <v>1768.15</v>
@@ -837,12 +853,12 @@
         <v>1764.18</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4">
-        <v>9308.200000000001</v>
+        <v>9308.2000000000007</v>
       </c>
       <c r="C4">
         <v>4282.2</v>
@@ -854,19 +870,19 @@
         <v>2513.63</v>
       </c>
       <c r="F4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K4">
         <v>1866.42</v>
@@ -875,15 +891,15 @@
         <v>1795.14</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>2702.5</v>
       </c>
       <c r="C5">
-        <v>5237.4</v>
+        <v>5237.3999999999996</v>
       </c>
       <c r="D5">
         <v>2260.54</v>
@@ -892,19 +908,19 @@
         <v>2174.61</v>
       </c>
       <c r="F5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K5">
         <v>1722.59</v>
@@ -913,9 +929,9 @@
         <v>1639.46</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>3602</v>
@@ -924,25 +940,25 @@
         <v>8728.1</v>
       </c>
       <c r="D6">
-        <v>2327.43</v>
+        <v>2327.4299999999998</v>
       </c>
       <c r="E6">
         <v>2295.79</v>
       </c>
       <c r="F6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H6" t="s">
         <v>116</v>
       </c>
-      <c r="H6" t="s">
-        <v>118</v>
-      </c>
       <c r="I6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K6">
         <v>1730.67</v>
@@ -951,9 +967,9 @@
         <v>1677.19</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>10482.6</v>
@@ -968,19 +984,19 @@
         <v>2520.35</v>
       </c>
       <c r="F7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I7" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" t="s">
         <v>121</v>
-      </c>
-      <c r="J7" t="s">
-        <v>123</v>
       </c>
       <c r="K7">
         <v>1860.82</v>
@@ -989,9 +1005,9 @@
         <v>1899.11</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>63.2</v>
@@ -1006,19 +1022,19 @@
         <v>2185.08</v>
       </c>
       <c r="F8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K8">
         <v>1747.89</v>
@@ -1027,36 +1043,36 @@
         <v>1694.98</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9">
-        <v>9854.700000000001</v>
+        <v>9854.7000000000007</v>
       </c>
       <c r="C9">
         <v>6836.8</v>
       </c>
       <c r="D9">
-        <v>2485.49</v>
+        <v>2485.4899999999998</v>
       </c>
       <c r="E9">
         <v>2429.08</v>
       </c>
       <c r="F9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K9">
         <v>1851.1</v>
@@ -1065,12 +1081,12 @@
         <v>1817.85</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10">
-        <v>9564.799999999999</v>
+        <v>9564.7999999999993</v>
       </c>
       <c r="C10">
         <v>3554.1</v>
@@ -1082,19 +1098,19 @@
         <v>2510.41</v>
       </c>
       <c r="F10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K10">
         <v>1869.46</v>
@@ -1103,9 +1119,9 @@
         <v>1890.18</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>5615.2</v>
@@ -1114,25 +1130,25 @@
         <v>5191</v>
       </c>
       <c r="D11">
-        <v>2379.26</v>
+        <v>2379.2600000000002</v>
       </c>
       <c r="E11">
-        <v>2378.2</v>
+        <v>2378.1999999999998</v>
       </c>
       <c r="F11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11" t="s">
         <v>112</v>
       </c>
-      <c r="G11" t="s">
-        <v>114</v>
-      </c>
       <c r="H11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K11">
         <v>1785.21</v>
@@ -1141,9 +1157,9 @@
         <v>1742.89</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>3636.4</v>
@@ -1158,19 +1174,19 @@
         <v>2238.4</v>
       </c>
       <c r="F12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K12">
         <v>1699.46</v>
@@ -1179,36 +1195,36 @@
         <v>1639.53</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>3341.1</v>
       </c>
       <c r="C13">
-        <v>9091.799999999999</v>
+        <v>9091.7999999999993</v>
       </c>
       <c r="D13">
         <v>2325.29</v>
       </c>
       <c r="E13">
-        <v>2291.68</v>
+        <v>2291.6799999999998</v>
       </c>
       <c r="F13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K13">
         <v>1763.69</v>
@@ -1217,9 +1233,9 @@
         <v>1733.07</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B14">
         <v>3058.4</v>
@@ -1234,19 +1250,19 @@
         <v>2441.9</v>
       </c>
       <c r="F14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I14" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K14">
         <v>1742.01</v>
@@ -1255,15 +1271,15 @@
         <v>1811.86</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <v>5340.9</v>
       </c>
       <c r="C15">
-        <v>9334.200000000001</v>
+        <v>9334.2000000000007</v>
       </c>
       <c r="D15">
         <v>2324.66</v>
@@ -1272,19 +1288,19 @@
         <v>2319.29</v>
       </c>
       <c r="F15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I15" t="s">
+        <v>119</v>
+      </c>
+      <c r="J15" t="s">
         <v>121</v>
-      </c>
-      <c r="J15" t="s">
-        <v>123</v>
       </c>
       <c r="K15">
         <v>1728.57</v>
@@ -1293,9 +1309,9 @@
         <v>1701.43</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>6054.6</v>
@@ -1310,19 +1326,19 @@
         <v>2499.75</v>
       </c>
       <c r="F16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" t="s">
         <v>112</v>
       </c>
-      <c r="G16" t="s">
-        <v>114</v>
-      </c>
       <c r="H16" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K16">
         <v>1805</v>
@@ -1331,9 +1347,9 @@
         <v>1850.8</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>6642</v>
@@ -1342,25 +1358,25 @@
         <v>7529.8</v>
       </c>
       <c r="D17">
-        <v>2362.32</v>
+        <v>2362.3200000000002</v>
       </c>
       <c r="E17">
-        <v>2343.22</v>
+        <v>2343.2199999999998</v>
       </c>
       <c r="F17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H17" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K17">
         <v>1711.34</v>
@@ -1369,9 +1385,9 @@
         <v>1804.52</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <v>11946</v>
@@ -1380,25 +1396,25 @@
         <v>8105.3</v>
       </c>
       <c r="D18">
-        <v>2472.95</v>
+        <v>2472.9499999999998</v>
       </c>
       <c r="E18">
-        <v>2415.28</v>
+        <v>2415.2800000000002</v>
       </c>
       <c r="F18" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" t="s">
         <v>113</v>
       </c>
-      <c r="G18" t="s">
-        <v>115</v>
-      </c>
       <c r="H18" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K18">
         <v>1813.15</v>
@@ -1407,9 +1423,9 @@
         <v>1765.2</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B19">
         <v>9511.9</v>
@@ -1424,19 +1440,19 @@
         <v>2448.64</v>
       </c>
       <c r="F19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H19" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I19" t="s">
+        <v>119</v>
+      </c>
+      <c r="J19" t="s">
         <v>121</v>
-      </c>
-      <c r="J19" t="s">
-        <v>123</v>
       </c>
       <c r="K19">
         <v>1877.79</v>
@@ -1445,9 +1461,9 @@
         <v>1810.96</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B20">
         <v>7466.2</v>
@@ -1462,19 +1478,19 @@
         <v>2501.31</v>
       </c>
       <c r="F20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G20" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I20" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K20">
         <v>1813.67</v>
@@ -1483,9 +1499,9 @@
         <v>1844.18</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B21">
         <v>11867.5</v>
@@ -1497,22 +1513,22 @@
         <v>2483.19</v>
       </c>
       <c r="E21">
-        <v>2438.3</v>
+        <v>2438.3000000000002</v>
       </c>
       <c r="F21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J21" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K21">
         <v>1789.04</v>
@@ -1521,15 +1537,15 @@
         <v>1816.81</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B22">
-        <v>2583.7</v>
+        <v>2583.6999999999998</v>
       </c>
       <c r="C22">
-        <v>142.7</v>
+        <v>142.69999999999999</v>
       </c>
       <c r="D22">
         <v>2457.11</v>
@@ -1538,19 +1554,19 @@
         <v>2484.59</v>
       </c>
       <c r="F22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G22" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J22" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K22">
         <v>1805.4</v>
@@ -1559,9 +1575,9 @@
         <v>1861.81</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B23">
         <v>1922.5</v>
@@ -1576,19 +1592,19 @@
         <v>2179.88</v>
       </c>
       <c r="F23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G23" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H23" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K23">
         <v>1719.56</v>
@@ -1597,9 +1613,9 @@
         <v>1680.78</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B24">
         <v>7350.5</v>
@@ -1608,25 +1624,25 @@
         <v>7930.2</v>
       </c>
       <c r="D24">
-        <v>2361.49</v>
+        <v>2361.4899999999998</v>
       </c>
       <c r="E24">
-        <v>2374.57</v>
+        <v>2374.5700000000002</v>
       </c>
       <c r="F24" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" t="s">
         <v>112</v>
       </c>
-      <c r="G24" t="s">
-        <v>114</v>
-      </c>
       <c r="H24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I24" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K24">
         <v>1762.46</v>
@@ -1635,12 +1651,12 @@
         <v>1818.49</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B25">
-        <v>527.3</v>
+        <v>527.29999999999995</v>
       </c>
       <c r="C25">
         <v>5130</v>
@@ -1652,19 +1668,19 @@
         <v>2190.77</v>
       </c>
       <c r="F25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H25" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I25" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J25" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K25">
         <v>1702.52</v>
@@ -1673,9 +1689,9 @@
         <v>1632.66</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B26">
         <v>428.2</v>
@@ -1690,19 +1706,19 @@
         <v>2149.38</v>
       </c>
       <c r="F26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I26" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K26">
         <v>1649.23</v>
@@ -1711,15 +1727,15 @@
         <v>1622.58</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B27">
         <v>6178.7</v>
       </c>
       <c r="C27">
-        <v>2264.2</v>
+        <v>2264.1999999999998</v>
       </c>
       <c r="D27">
         <v>2433.75</v>
@@ -1728,19 +1744,19 @@
         <v>2460.33</v>
       </c>
       <c r="F27" t="s">
+        <v>110</v>
+      </c>
+      <c r="G27" t="s">
         <v>112</v>
       </c>
-      <c r="G27" t="s">
-        <v>114</v>
-      </c>
       <c r="H27" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I27" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J27" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K27">
         <v>1809.04</v>
@@ -1749,9 +1765,9 @@
         <v>1841.29</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B28">
         <v>5594.5</v>
@@ -1760,25 +1776,25 @@
         <v>1985.2</v>
       </c>
       <c r="D28">
-        <v>2443.45</v>
+        <v>2443.4499999999998</v>
       </c>
       <c r="E28">
-        <v>2454.26</v>
+        <v>2454.2600000000002</v>
       </c>
       <c r="F28" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28" t="s">
         <v>112</v>
       </c>
-      <c r="G28" t="s">
-        <v>114</v>
-      </c>
       <c r="H28" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J28" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K28">
         <v>1813.72</v>
@@ -1787,9 +1803,9 @@
         <v>1789.21</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B29">
         <v>11006</v>
@@ -1804,19 +1820,19 @@
         <v>2502</v>
       </c>
       <c r="F29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I29" t="s">
+        <v>119</v>
+      </c>
+      <c r="J29" t="s">
         <v>121</v>
-      </c>
-      <c r="J29" t="s">
-        <v>123</v>
       </c>
       <c r="K29">
         <v>1885.5</v>
@@ -1825,9 +1841,9 @@
         <v>1809.5</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B30">
         <v>7550.7</v>
@@ -1836,25 +1852,25 @@
         <v>1794.1</v>
       </c>
       <c r="D30">
-        <v>2467.49</v>
+        <v>2467.4899999999998</v>
       </c>
       <c r="E30">
-        <v>2470.07</v>
+        <v>2470.0700000000002</v>
       </c>
       <c r="F30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G30" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H30" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K30">
         <v>1853.22</v>
@@ -1863,9 +1879,9 @@
         <v>1812.85</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B31">
         <v>6169.4</v>
@@ -1877,22 +1893,22 @@
         <v>2430.09</v>
       </c>
       <c r="E31">
-        <v>2438.26</v>
+        <v>2438.2600000000002</v>
       </c>
       <c r="F31" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" t="s">
         <v>112</v>
       </c>
-      <c r="G31" t="s">
-        <v>114</v>
-      </c>
       <c r="H31" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I31" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J31" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K31">
         <v>1812.14</v>
@@ -1901,15 +1917,15 @@
         <v>1811.62</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B32">
         <v>5962.5</v>
       </c>
       <c r="C32">
-        <v>9481.200000000001</v>
+        <v>9481.2000000000007</v>
       </c>
       <c r="D32">
         <v>2314.11</v>
@@ -1918,19 +1934,19 @@
         <v>2336.69</v>
       </c>
       <c r="F32" t="s">
+        <v>110</v>
+      </c>
+      <c r="G32" t="s">
         <v>112</v>
       </c>
-      <c r="G32" t="s">
-        <v>114</v>
-      </c>
       <c r="H32" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I32" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J32" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K32">
         <v>1687.72</v>
@@ -1939,9 +1955,9 @@
         <v>1724.68</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B33">
         <v>2970.2</v>
@@ -1950,25 +1966,25 @@
         <v>5733.3</v>
       </c>
       <c r="D33">
-        <v>2265.05</v>
+        <v>2265.0500000000002</v>
       </c>
       <c r="E33">
         <v>2193.66</v>
       </c>
       <c r="F33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G33" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H33" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I33" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J33" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K33">
         <v>1666.57</v>
@@ -1977,9 +1993,9 @@
         <v>1688.65</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B34">
         <v>141.5</v>
@@ -1988,25 +2004,25 @@
         <v>3400.7</v>
       </c>
       <c r="D34">
-        <v>2288.22</v>
+        <v>2288.2199999999998</v>
       </c>
       <c r="E34">
-        <v>2224.93</v>
+        <v>2224.9299999999998</v>
       </c>
       <c r="F34" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G34" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H34" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I34" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J34" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K34">
         <v>1688.28</v>
@@ -2015,12 +2031,12 @@
         <v>1736.79</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B35">
-        <v>2308.8</v>
+        <v>2308.8000000000002</v>
       </c>
       <c r="C35">
         <v>2715.2</v>
@@ -2029,22 +2045,22 @@
         <v>2350.08</v>
       </c>
       <c r="E35">
-        <v>2311.55</v>
+        <v>2311.5500000000002</v>
       </c>
       <c r="F35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H35" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I35" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J35" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K35">
         <v>1759.07</v>
@@ -2053,9 +2069,9 @@
         <v>1661.25</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B36">
         <v>8304.4</v>
@@ -2070,19 +2086,19 @@
         <v>2362.9</v>
       </c>
       <c r="F36" t="s">
+        <v>111</v>
+      </c>
+      <c r="G36" t="s">
         <v>113</v>
       </c>
-      <c r="G36" t="s">
-        <v>115</v>
-      </c>
       <c r="H36" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I36" t="s">
+        <v>119</v>
+      </c>
+      <c r="J36" t="s">
         <v>121</v>
-      </c>
-      <c r="J36" t="s">
-        <v>123</v>
       </c>
       <c r="K36">
         <v>1714.47</v>
@@ -2091,12 +2107,12 @@
         <v>1669.41</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B37">
-        <v>2407.3</v>
+        <v>2407.3000000000002</v>
       </c>
       <c r="C37">
         <v>4444.8</v>
@@ -2108,19 +2124,19 @@
         <v>2224.52</v>
       </c>
       <c r="F37" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G37" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H37" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I37" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J37" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K37">
         <v>1749.66</v>
@@ -2129,12 +2145,12 @@
         <v>1711.97</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B38">
-        <v>4434.4</v>
+        <v>4434.3999999999996</v>
       </c>
       <c r="C38">
         <v>9803.9</v>
@@ -2146,19 +2162,19 @@
         <v>2329.12</v>
       </c>
       <c r="F38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G38" t="s">
         <v>112</v>
       </c>
-      <c r="G38" t="s">
-        <v>114</v>
-      </c>
       <c r="H38" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I38" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J38" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K38">
         <v>1744.29</v>
@@ -2167,9 +2183,9 @@
         <v>1709.03</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B39">
         <v>44.8</v>
@@ -2184,19 +2200,19 @@
         <v>2219.35</v>
       </c>
       <c r="F39" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G39" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H39" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K39">
         <v>1722.67</v>
@@ -2205,9 +2221,9 @@
         <v>1736.36</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B40">
         <v>9960.6</v>
@@ -2216,25 +2232,25 @@
         <v>5211.7</v>
       </c>
       <c r="D40">
-        <v>2511.22</v>
+        <v>2511.2199999999998</v>
       </c>
       <c r="E40">
-        <v>2463.74</v>
+        <v>2463.7399999999998</v>
       </c>
       <c r="F40" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G40" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I40" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J40" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K40">
         <v>1856.1</v>
@@ -2243,9 +2259,9 @@
         <v>1922.5</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B41">
         <v>1853.5</v>
@@ -2260,19 +2276,19 @@
         <v>2220.42</v>
       </c>
       <c r="F41" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G41" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H41" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I41" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J41" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K41">
         <v>1726.86</v>
@@ -2281,9 +2297,9 @@
         <v>1675.03</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B42">
         <v>3211.2</v>
@@ -2298,19 +2314,19 @@
         <v>2233.29</v>
       </c>
       <c r="F42" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G42" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H42" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I42" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J42" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K42">
         <v>1683.8</v>
@@ -2319,9 +2335,9 @@
         <v>1672.77</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B43">
         <v>10564</v>
@@ -2330,25 +2346,25 @@
         <v>5806.5</v>
       </c>
       <c r="D43">
-        <v>2506.97</v>
+        <v>2506.9699999999998</v>
       </c>
       <c r="E43">
-        <v>2457.53</v>
+        <v>2457.5300000000002</v>
       </c>
       <c r="F43" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G43" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H43" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I43" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J43" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K43">
         <v>1899.55</v>
@@ -2357,9 +2373,9 @@
         <v>1807.8</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B44">
         <v>6117.5</v>
@@ -2374,19 +2390,19 @@
         <v>2410.86</v>
       </c>
       <c r="F44" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G44" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H44" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I44" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J44" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K44">
         <v>1825.81</v>
@@ -2395,12 +2411,12 @@
         <v>1794.44</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B45">
-        <v>10165.8</v>
+        <v>10165.799999999999</v>
       </c>
       <c r="C45">
         <v>8781.9</v>
@@ -2409,22 +2425,22 @@
         <v>2405.04</v>
       </c>
       <c r="E45">
-        <v>2398.82</v>
+        <v>2398.8200000000002</v>
       </c>
       <c r="F45" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G45" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H45" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I45" t="s">
+        <v>119</v>
+      </c>
+      <c r="J45" t="s">
         <v>121</v>
-      </c>
-      <c r="J45" t="s">
-        <v>123</v>
       </c>
       <c r="K45">
         <v>1821.31</v>
@@ -2433,9 +2449,9 @@
         <v>1775.39</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B46">
         <v>7676.6</v>
@@ -2447,22 +2463,22 @@
         <v>2498</v>
       </c>
       <c r="E46">
-        <v>2557.55</v>
+        <v>2557.5500000000002</v>
       </c>
       <c r="F46" t="s">
+        <v>110</v>
+      </c>
+      <c r="G46" t="s">
         <v>112</v>
       </c>
-      <c r="G46" t="s">
-        <v>114</v>
-      </c>
       <c r="H46" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I46" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J46" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K46">
         <v>1809.07</v>
@@ -2471,12 +2487,12 @@
         <v>1824.73</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B47">
-        <v>8901.299999999999</v>
+        <v>8901.2999999999993</v>
       </c>
       <c r="C47">
         <v>9227.6</v>
@@ -2488,19 +2504,19 @@
         <v>2380.16</v>
       </c>
       <c r="F47" t="s">
+        <v>111</v>
+      </c>
+      <c r="G47" t="s">
         <v>113</v>
       </c>
-      <c r="G47" t="s">
-        <v>115</v>
-      </c>
       <c r="H47" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I47" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J47" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K47">
         <v>1701.05</v>
@@ -2509,12 +2525,12 @@
         <v>1783.29</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B48">
-        <v>1097.9</v>
+        <v>1097.9000000000001</v>
       </c>
       <c r="C48">
         <v>687.2</v>
@@ -2523,22 +2539,22 @@
         <v>2390.37</v>
       </c>
       <c r="E48">
-        <v>2388.82</v>
+        <v>2388.8200000000002</v>
       </c>
       <c r="F48" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G48" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H48" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I48" t="s">
+        <v>119</v>
+      </c>
+      <c r="J48" t="s">
         <v>121</v>
-      </c>
-      <c r="J48" t="s">
-        <v>123</v>
       </c>
       <c r="K48">
         <v>1732.24</v>
@@ -2547,9 +2563,9 @@
         <v>1693.6</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B49">
         <v>6493.7</v>
@@ -2558,25 +2574,25 @@
         <v>4300</v>
       </c>
       <c r="D49">
-        <v>2442.24</v>
+        <v>2442.2399999999998</v>
       </c>
       <c r="E49">
         <v>2439.17</v>
       </c>
       <c r="F49" t="s">
+        <v>110</v>
+      </c>
+      <c r="G49" t="s">
         <v>112</v>
       </c>
-      <c r="G49" t="s">
-        <v>114</v>
-      </c>
       <c r="H49" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I49" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J49" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K49">
         <v>1771.79</v>
@@ -2585,36 +2601,36 @@
         <v>1813.69</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B50">
         <v>6093.3</v>
       </c>
       <c r="C50">
-        <v>5195.1</v>
+        <v>5195.1000000000004</v>
       </c>
       <c r="D50">
-        <v>2420.2</v>
+        <v>2420.1999999999998</v>
       </c>
       <c r="E50">
         <v>2428.61</v>
       </c>
       <c r="F50" t="s">
+        <v>110</v>
+      </c>
+      <c r="G50" t="s">
         <v>112</v>
       </c>
-      <c r="G50" t="s">
-        <v>114</v>
-      </c>
       <c r="H50" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I50" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J50" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K50">
         <v>1812.13</v>
@@ -2623,9 +2639,9 @@
         <v>1796.79</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B51">
         <v>10456.1</v>
@@ -2634,25 +2650,25 @@
         <v>9509.4</v>
       </c>
       <c r="D51">
-        <v>2402.05</v>
+        <v>2402.0500000000002</v>
       </c>
       <c r="E51">
         <v>2383.61</v>
       </c>
       <c r="F51" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G51" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H51" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I51" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J51" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K51">
         <v>1803.02</v>
@@ -2661,9 +2677,9 @@
         <v>1819.77</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B52">
         <v>4335.2</v>
@@ -2678,19 +2694,19 @@
         <v>2365.62</v>
       </c>
       <c r="F52" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G52" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H52" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I52" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J52" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K52">
         <v>1810.48</v>
@@ -2699,9 +2715,9 @@
         <v>1765.81</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B53">
         <v>7178.2</v>
@@ -2713,22 +2729,22 @@
         <v>2358.94</v>
       </c>
       <c r="E53">
-        <v>2366.2</v>
+        <v>2366.1999999999998</v>
       </c>
       <c r="F53" t="s">
+        <v>110</v>
+      </c>
+      <c r="G53" t="s">
         <v>112</v>
       </c>
-      <c r="G53" t="s">
-        <v>114</v>
-      </c>
       <c r="H53" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I53" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J53" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K53">
         <v>1813.39</v>
@@ -2737,9 +2753,9 @@
         <v>1778.6</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B54">
         <v>711</v>
@@ -2751,22 +2767,22 @@
         <v>2231.77</v>
       </c>
       <c r="E54">
-        <v>2149.76</v>
+        <v>2149.7600000000002</v>
       </c>
       <c r="F54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G54" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H54" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I54" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J54" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K54">
         <v>1700.77</v>
@@ -2775,12 +2791,12 @@
         <v>1604.42</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B55">
-        <v>4651.6</v>
+        <v>4651.6000000000004</v>
       </c>
       <c r="C55">
         <v>7170.9</v>
@@ -2792,19 +2808,19 @@
         <v>2317.02</v>
       </c>
       <c r="F55" t="s">
+        <v>110</v>
+      </c>
+      <c r="G55" t="s">
         <v>112</v>
       </c>
-      <c r="G55" t="s">
-        <v>114</v>
-      </c>
       <c r="H55" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I55" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J55" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K55">
         <v>1737.01</v>
@@ -2813,9 +2829,9 @@
         <v>1740.12</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B56">
         <v>3876.4</v>
@@ -2827,22 +2843,22 @@
         <v>2296.63</v>
       </c>
       <c r="E56">
-        <v>2223.47</v>
+        <v>2223.4699999999998</v>
       </c>
       <c r="F56" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G56" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H56" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I56" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J56" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K56">
         <v>1712.57</v>
@@ -2851,9 +2867,9 @@
         <v>1712.32</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B57">
         <v>1802.4</v>
@@ -2868,19 +2884,19 @@
         <v>2226.79</v>
       </c>
       <c r="F57" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G57" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H57" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I57" t="s">
+        <v>119</v>
+      </c>
+      <c r="J57" t="s">
         <v>121</v>
-      </c>
-      <c r="J57" t="s">
-        <v>123</v>
       </c>
       <c r="K57">
         <v>1707.95</v>
@@ -2889,9 +2905,9 @@
         <v>1723.61</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B58">
         <v>9796.1</v>
@@ -2900,25 +2916,25 @@
         <v>3326.8</v>
       </c>
       <c r="D58">
-        <v>2530.57</v>
+        <v>2530.5700000000002</v>
       </c>
       <c r="E58">
-        <v>2488.43</v>
+        <v>2488.4299999999998</v>
       </c>
       <c r="F58" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G58" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H58" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I58" t="s">
+        <v>119</v>
+      </c>
+      <c r="J58" t="s">
         <v>121</v>
-      </c>
-      <c r="J58" t="s">
-        <v>123</v>
       </c>
       <c r="K58">
         <v>1814.87</v>
@@ -2927,12 +2943,12 @@
         <v>1828.76</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B59">
-        <v>4553.4</v>
+        <v>4553.3999999999996</v>
       </c>
       <c r="C59">
         <v>3982.8</v>
@@ -2944,19 +2960,19 @@
         <v>2357.29</v>
       </c>
       <c r="F59" t="s">
+        <v>110</v>
+      </c>
+      <c r="G59" t="s">
         <v>112</v>
       </c>
-      <c r="G59" t="s">
-        <v>114</v>
-      </c>
       <c r="H59" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I59" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J59" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K59">
         <v>1765.43</v>
@@ -2965,9 +2981,9 @@
         <v>1816.46</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B60">
         <v>11745</v>
@@ -2976,25 +2992,25 @@
         <v>2029.1</v>
       </c>
       <c r="D60">
-        <v>2571.26</v>
+        <v>2571.2600000000002</v>
       </c>
       <c r="E60">
         <v>2599.81</v>
       </c>
       <c r="F60" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G60" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H60" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I60" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J60" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K60">
         <v>1875.28</v>
@@ -3003,9 +3019,9 @@
         <v>1930.66</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B61">
         <v>7079.9</v>
@@ -3017,22 +3033,22 @@
         <v>2466.37</v>
       </c>
       <c r="E61">
-        <v>2491.49</v>
+        <v>2491.4899999999998</v>
       </c>
       <c r="F61" t="s">
+        <v>110</v>
+      </c>
+      <c r="G61" t="s">
         <v>112</v>
       </c>
-      <c r="G61" t="s">
-        <v>114</v>
-      </c>
       <c r="H61" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I61" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J61" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K61">
         <v>1801.81</v>
@@ -3041,9 +3057,9 @@
         <v>1800.49</v>
       </c>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B62">
         <v>7260.7</v>
@@ -3058,19 +3074,19 @@
         <v>2479.81</v>
       </c>
       <c r="F62" t="s">
+        <v>110</v>
+      </c>
+      <c r="G62" t="s">
         <v>112</v>
       </c>
-      <c r="G62" t="s">
-        <v>114</v>
-      </c>
       <c r="H62" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I62" t="s">
+        <v>119</v>
+      </c>
+      <c r="J62" t="s">
         <v>121</v>
-      </c>
-      <c r="J62" t="s">
-        <v>123</v>
       </c>
       <c r="K62">
         <v>1790.01</v>
@@ -3079,9 +3095,9 @@
         <v>1724.06</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B63">
         <v>7656</v>
@@ -3096,19 +3112,19 @@
         <v>2322.91</v>
       </c>
       <c r="F63" t="s">
+        <v>110</v>
+      </c>
+      <c r="G63" t="s">
         <v>112</v>
       </c>
-      <c r="G63" t="s">
-        <v>114</v>
-      </c>
       <c r="H63" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I63" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J63" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K63">
         <v>1751.85</v>
@@ -3117,36 +3133,36 @@
         <v>1694.01</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B64">
         <v>8117.4</v>
       </c>
       <c r="C64">
-        <v>8401.700000000001</v>
+        <v>8401.7000000000007</v>
       </c>
       <c r="D64">
         <v>2364.14</v>
       </c>
       <c r="E64">
-        <v>2362.82</v>
+        <v>2362.8200000000002</v>
       </c>
       <c r="F64" t="s">
+        <v>110</v>
+      </c>
+      <c r="G64" t="s">
         <v>112</v>
       </c>
-      <c r="G64" t="s">
-        <v>114</v>
-      </c>
       <c r="H64" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I64" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J64" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K64">
         <v>1793.73</v>
@@ -3155,36 +3171,36 @@
         <v>1760.63</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B65">
         <v>1809.5</v>
       </c>
       <c r="C65">
-        <v>1124.1</v>
+        <v>1124.0999999999999</v>
       </c>
       <c r="D65">
-        <v>2405.53</v>
+        <v>2405.5300000000002</v>
       </c>
       <c r="E65">
-        <v>2401.47</v>
+        <v>2401.4699999999998</v>
       </c>
       <c r="F65" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G65" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H65" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I65" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J65" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K65">
         <v>1782.89</v>
@@ -3193,9 +3209,9 @@
         <v>1784.73</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B66">
         <v>5283.8</v>
@@ -3207,22 +3223,22 @@
         <v>2364.19</v>
       </c>
       <c r="E66">
-        <v>2353.01</v>
+        <v>2353.0100000000002</v>
       </c>
       <c r="F66" t="s">
+        <v>110</v>
+      </c>
+      <c r="G66" t="s">
         <v>112</v>
       </c>
-      <c r="G66" t="s">
-        <v>114</v>
-      </c>
       <c r="H66" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I66" t="s">
+        <v>119</v>
+      </c>
+      <c r="J66" t="s">
         <v>121</v>
-      </c>
-      <c r="J66" t="s">
-        <v>123</v>
       </c>
       <c r="K66">
         <v>1766.33</v>
@@ -3231,9 +3247,9 @@
         <v>1741.36</v>
       </c>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B67">
         <v>2874.8</v>
@@ -3242,25 +3258,25 @@
         <v>4792</v>
       </c>
       <c r="D67">
-        <v>2284.05</v>
+        <v>2284.0500000000002</v>
       </c>
       <c r="E67">
         <v>2216.94</v>
       </c>
       <c r="F67" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G67" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H67" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I67" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J67" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K67">
         <v>1700.76</v>
@@ -3269,9 +3285,9 @@
         <v>1662.32</v>
       </c>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B68">
         <v>4830</v>
@@ -3280,25 +3296,25 @@
         <v>5946.8</v>
       </c>
       <c r="D68">
-        <v>2340.2</v>
+        <v>2340.1999999999998</v>
       </c>
       <c r="E68">
-        <v>2332.07</v>
+        <v>2332.0700000000002</v>
       </c>
       <c r="F68" t="s">
+        <v>110</v>
+      </c>
+      <c r="G68" t="s">
         <v>112</v>
       </c>
-      <c r="G68" t="s">
-        <v>114</v>
-      </c>
       <c r="H68" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I68" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J68" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K68">
         <v>1739.19</v>
@@ -3307,36 +3323,36 @@
         <v>1766.64</v>
       </c>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B69">
-        <v>1160.4</v>
+        <v>1160.4000000000001</v>
       </c>
       <c r="C69">
         <v>6592.8</v>
       </c>
       <c r="D69">
-        <v>2242.3</v>
+        <v>2242.3000000000002</v>
       </c>
       <c r="E69">
         <v>2168.79</v>
       </c>
       <c r="F69" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G69" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H69" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I69" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J69" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K69">
         <v>1684.11</v>
@@ -3345,9 +3361,9 @@
         <v>1628.98</v>
       </c>
     </row>
-    <row r="70" spans="1:12">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B70">
         <v>11613.9</v>
@@ -3362,19 +3378,19 @@
         <v>2549.62</v>
       </c>
       <c r="F70" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G70" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H70" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I70" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J70" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K70">
         <v>1850.74</v>
@@ -3383,9 +3399,9 @@
         <v>1773.27</v>
       </c>
     </row>
-    <row r="71" spans="1:12">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B71">
         <v>2580</v>
@@ -3397,22 +3413,22 @@
         <v>2298.59</v>
       </c>
       <c r="E71">
-        <v>2255.05</v>
+        <v>2255.0500000000002</v>
       </c>
       <c r="F71" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G71" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H71" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I71" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J71" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K71">
         <v>1707.35</v>
@@ -3421,15 +3437,15 @@
         <v>1687.58</v>
       </c>
     </row>
-    <row r="72" spans="1:12">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B72">
         <v>8061.2</v>
       </c>
       <c r="C72">
-        <v>4658.4</v>
+        <v>4658.3999999999996</v>
       </c>
       <c r="D72">
         <v>2510.56</v>
@@ -3438,19 +3454,19 @@
         <v>2558.36</v>
       </c>
       <c r="F72" t="s">
+        <v>110</v>
+      </c>
+      <c r="G72" t="s">
         <v>112</v>
       </c>
-      <c r="G72" t="s">
-        <v>114</v>
-      </c>
       <c r="H72" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I72" t="s">
+        <v>119</v>
+      </c>
+      <c r="J72" t="s">
         <v>121</v>
-      </c>
-      <c r="J72" t="s">
-        <v>123</v>
       </c>
       <c r="K72">
         <v>1846.26</v>
@@ -3459,9 +3475,9 @@
         <v>1899.62</v>
       </c>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B73">
         <v>3605</v>
@@ -3470,25 +3486,25 @@
         <v>6281</v>
       </c>
       <c r="D73">
-        <v>2282.55</v>
+        <v>2282.5500000000002</v>
       </c>
       <c r="E73">
         <v>2226.42</v>
       </c>
       <c r="F73" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G73" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H73" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I73" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J73" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K73">
         <v>1749.52</v>
@@ -3497,9 +3513,9 @@
         <v>1650.87</v>
       </c>
     </row>
-    <row r="74" spans="1:12">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B74">
         <v>10488.9</v>
@@ -3508,25 +3524,25 @@
         <v>6352.3</v>
       </c>
       <c r="D74">
-        <v>2492.53</v>
+        <v>2492.5300000000002</v>
       </c>
       <c r="E74">
         <v>2429.75</v>
       </c>
       <c r="F74" t="s">
+        <v>111</v>
+      </c>
+      <c r="G74" t="s">
         <v>113</v>
       </c>
-      <c r="G74" t="s">
-        <v>115</v>
-      </c>
       <c r="H74" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I74" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J74" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K74">
         <v>1800.88</v>
@@ -3535,9 +3551,9 @@
         <v>1818.28</v>
       </c>
     </row>
-    <row r="75" spans="1:12">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B75">
         <v>7946.6</v>
@@ -3549,22 +3565,22 @@
         <v>2471.84</v>
       </c>
       <c r="E75">
-        <v>2494.47</v>
+        <v>2494.4699999999998</v>
       </c>
       <c r="F75" t="s">
+        <v>110</v>
+      </c>
+      <c r="G75" t="s">
         <v>112</v>
       </c>
-      <c r="G75" t="s">
-        <v>114</v>
-      </c>
       <c r="H75" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I75" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J75" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K75">
         <v>1853.08</v>
@@ -3573,36 +3589,36 @@
         <v>1849.59</v>
       </c>
     </row>
-    <row r="76" spans="1:12">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B76">
         <v>1579.4</v>
       </c>
       <c r="C76">
-        <v>618.7</v>
+        <v>618.70000000000005</v>
       </c>
       <c r="D76">
         <v>2402.75</v>
       </c>
       <c r="E76">
-        <v>2405.07</v>
+        <v>2405.0700000000002</v>
       </c>
       <c r="F76" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G76" t="s">
+        <v>114</v>
+      </c>
+      <c r="H76" t="s">
         <v>116</v>
       </c>
-      <c r="H76" t="s">
-        <v>118</v>
-      </c>
       <c r="I76" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J76" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K76">
         <v>1768.42</v>
@@ -3611,9 +3627,9 @@
         <v>1779.83</v>
       </c>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B77">
         <v>10140.9</v>
@@ -3622,25 +3638,25 @@
         <v>4115.2</v>
       </c>
       <c r="D77">
-        <v>2545.32</v>
+        <v>2545.3200000000002</v>
       </c>
       <c r="E77">
         <v>2513.71</v>
       </c>
       <c r="F77" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G77" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H77" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I77" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J77" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K77">
         <v>1843.65</v>
@@ -3649,9 +3665,9 @@
         <v>1853.09</v>
       </c>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B78">
         <v>11339.4</v>
@@ -3666,19 +3682,19 @@
         <v>2424.04</v>
       </c>
       <c r="F78" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G78" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H78" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I78" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J78" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K78">
         <v>1764.78</v>
@@ -3687,9 +3703,9 @@
         <v>1754.93</v>
       </c>
     </row>
-    <row r="79" spans="1:12">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B79">
         <v>10847</v>
@@ -3704,19 +3720,19 @@
         <v>2412.59</v>
       </c>
       <c r="F79" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G79" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H79" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I79" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J79" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K79">
         <v>1737.97</v>
@@ -3725,9 +3741,9 @@
         <v>1786.78</v>
       </c>
     </row>
-    <row r="80" spans="1:12">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B80">
         <v>6836.6</v>
@@ -3742,19 +3758,19 @@
         <v>2390.09</v>
       </c>
       <c r="F80" t="s">
+        <v>110</v>
+      </c>
+      <c r="G80" t="s">
         <v>112</v>
       </c>
-      <c r="G80" t="s">
-        <v>114</v>
-      </c>
       <c r="H80" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I80" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J80" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K80">
         <v>1793.28</v>
@@ -3763,9 +3779,9 @@
         <v>1830.65</v>
       </c>
     </row>
-    <row r="81" spans="1:12">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B81">
         <v>1745.5</v>
@@ -3780,19 +3796,19 @@
         <v>2413.04</v>
       </c>
       <c r="F81" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G81" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H81" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I81" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J81" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K81">
         <v>1751.37</v>
@@ -3801,9 +3817,9 @@
         <v>1781.73</v>
       </c>
     </row>
-    <row r="82" spans="1:12">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B82">
         <v>2309.6</v>
@@ -3818,19 +3834,19 @@
         <v>2223.83</v>
       </c>
       <c r="F82" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G82" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H82" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I82" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J82" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K82">
         <v>1734.13</v>
@@ -3839,9 +3855,9 @@
         <v>1639.69</v>
       </c>
     </row>
-    <row r="83" spans="1:12">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B83">
         <v>11134.9</v>
@@ -3850,25 +3866,25 @@
         <v>8020.4</v>
       </c>
       <c r="D83">
-        <v>2464.82</v>
+        <v>2464.8200000000002</v>
       </c>
       <c r="E83">
-        <v>2406.45</v>
+        <v>2406.4499999999998</v>
       </c>
       <c r="F83" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G83" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H83" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I83" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J83" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K83">
         <v>1813.23</v>
@@ -3877,9 +3893,9 @@
         <v>1837.91</v>
       </c>
     </row>
-    <row r="84" spans="1:12">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B84">
         <v>6627.9</v>
@@ -3894,19 +3910,19 @@
         <v>2320.86</v>
       </c>
       <c r="F84" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G84" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I84" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J84" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K84">
         <v>1748.8</v>
@@ -3915,9 +3931,9 @@
         <v>1682.68</v>
       </c>
     </row>
-    <row r="85" spans="1:12">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B85">
         <v>2166.6</v>
@@ -3932,19 +3948,19 @@
         <v>2191.88</v>
       </c>
       <c r="F85" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G85" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H85" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I85" t="s">
+        <v>119</v>
+      </c>
+      <c r="J85" t="s">
         <v>121</v>
-      </c>
-      <c r="J85" t="s">
-        <v>123</v>
       </c>
       <c r="K85">
         <v>1738.97</v>
@@ -3953,9 +3969,9 @@
         <v>1728.7</v>
       </c>
     </row>
-    <row r="86" spans="1:12">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B86">
         <v>10608.7</v>
@@ -3967,22 +3983,22 @@
         <v>2409.66</v>
       </c>
       <c r="E86">
-        <v>2398.99</v>
+        <v>2398.9899999999998</v>
       </c>
       <c r="F86" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G86" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H86" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I86" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J86" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K86">
         <v>1780.95</v>
@@ -3991,9 +4007,9 @@
         <v>1780.93</v>
       </c>
     </row>
-    <row r="87" spans="1:12">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B87">
         <v>7698.9</v>
@@ -4002,25 +4018,25 @@
         <v>466.5</v>
       </c>
       <c r="D87">
-        <v>2460.26</v>
+        <v>2460.2600000000002</v>
       </c>
       <c r="E87">
         <v>2476.91</v>
       </c>
       <c r="F87" t="s">
+        <v>110</v>
+      </c>
+      <c r="G87" t="s">
         <v>112</v>
       </c>
-      <c r="G87" t="s">
-        <v>114</v>
-      </c>
       <c r="H87" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I87" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J87" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K87">
         <v>1721.86</v>
@@ -4029,36 +4045,36 @@
         <v>1842.13</v>
       </c>
     </row>
-    <row r="88" spans="1:12">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B88">
         <v>6836.3</v>
       </c>
       <c r="C88">
-        <v>302.9</v>
+        <v>302.89999999999998</v>
       </c>
       <c r="D88">
         <v>2459.34</v>
       </c>
       <c r="E88">
-        <v>2488.2</v>
+        <v>2488.1999999999998</v>
       </c>
       <c r="F88" t="s">
+        <v>110</v>
+      </c>
+      <c r="G88" t="s">
         <v>112</v>
       </c>
-      <c r="G88" t="s">
-        <v>114</v>
-      </c>
       <c r="H88" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I88" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J88" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K88">
         <v>1762.36</v>
@@ -4067,9 +4083,9 @@
         <v>1837.76</v>
       </c>
     </row>
-    <row r="89" spans="1:12">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B89">
         <v>4515.5</v>
@@ -4078,25 +4094,25 @@
         <v>202.2</v>
       </c>
       <c r="D89">
-        <v>2484.7</v>
+        <v>2484.6999999999998</v>
       </c>
       <c r="E89">
         <v>2511.39</v>
       </c>
       <c r="F89" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G89" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H89" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I89" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J89" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K89">
         <v>1848.32</v>
@@ -4105,36 +4121,36 @@
         <v>1836.84</v>
       </c>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B90">
         <v>4931.5</v>
       </c>
       <c r="C90">
-        <v>2527.7</v>
+        <v>2527.6999999999998</v>
       </c>
       <c r="D90">
-        <v>2418.2</v>
+        <v>2418.1999999999998</v>
       </c>
       <c r="E90">
-        <v>2411.68</v>
+        <v>2411.6799999999998</v>
       </c>
       <c r="F90" t="s">
+        <v>110</v>
+      </c>
+      <c r="G90" t="s">
         <v>112</v>
       </c>
-      <c r="G90" t="s">
-        <v>114</v>
-      </c>
       <c r="H90" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I90" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J90" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K90">
         <v>1840.97</v>
@@ -4143,15 +4159,15 @@
         <v>1825.75</v>
       </c>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B91">
         <v>2873.9</v>
       </c>
       <c r="C91">
-        <v>2485.7</v>
+        <v>2485.6999999999998</v>
       </c>
       <c r="D91">
         <v>2372.36</v>
@@ -4160,19 +4176,19 @@
         <v>2354.25</v>
       </c>
       <c r="F91" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G91" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H91" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I91" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J91" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K91">
         <v>1760.5</v>
@@ -4181,9 +4197,9 @@
         <v>1750.41</v>
       </c>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B92">
         <v>456.7</v>
@@ -4195,22 +4211,22 @@
         <v>2344.11</v>
       </c>
       <c r="E92">
-        <v>2323.01</v>
+        <v>2323.0100000000002</v>
       </c>
       <c r="F92" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G92" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H92" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I92" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J92" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K92">
         <v>1729.12</v>
@@ -4219,9 +4235,9 @@
         <v>1704.92</v>
       </c>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B93">
         <v>10514.6</v>
@@ -4233,22 +4249,22 @@
         <v>2506.34</v>
       </c>
       <c r="E93">
-        <v>2458.26</v>
+        <v>2458.2600000000002</v>
       </c>
       <c r="F93" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G93" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H93" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I93" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J93" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K93">
         <v>1796.09</v>
@@ -4257,9 +4273,9 @@
         <v>1810.18</v>
       </c>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B94">
         <v>5612.8</v>
@@ -4274,19 +4290,19 @@
         <v>2468.48</v>
       </c>
       <c r="F94" t="s">
+        <v>110</v>
+      </c>
+      <c r="G94" t="s">
         <v>112</v>
       </c>
-      <c r="G94" t="s">
-        <v>114</v>
-      </c>
       <c r="H94" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I94" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J94" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K94">
         <v>1825.98</v>
@@ -4295,9 +4311,9 @@
         <v>1746.17</v>
       </c>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B95">
         <v>6571.6</v>
@@ -4306,25 +4322,25 @@
         <v>5903.9</v>
       </c>
       <c r="D95">
-        <v>2408.28</v>
+        <v>2408.2800000000002</v>
       </c>
       <c r="E95">
         <v>2422.61</v>
       </c>
       <c r="F95" t="s">
+        <v>110</v>
+      </c>
+      <c r="G95" t="s">
         <v>112</v>
       </c>
-      <c r="G95" t="s">
-        <v>114</v>
-      </c>
       <c r="H95" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I95" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J95" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K95">
         <v>1733.92</v>
@@ -4333,9 +4349,9 @@
         <v>1784.18</v>
       </c>
     </row>
-    <row r="96" spans="1:12">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B96">
         <v>3866</v>
@@ -4350,19 +4366,19 @@
         <v>2470.23</v>
       </c>
       <c r="F96" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G96" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H96" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I96" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J96" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K96">
         <v>1765.93</v>
@@ -4371,9 +4387,9 @@
         <v>1746.04</v>
       </c>
     </row>
-    <row r="97" spans="1:12">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B97">
         <v>9015.9</v>
@@ -4388,19 +4404,19 @@
         <v>2427.46</v>
       </c>
       <c r="F97" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G97" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H97" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I97" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J97" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K97">
         <v>1817.56</v>
@@ -4409,12 +4425,12 @@
         <v>1793.23</v>
       </c>
     </row>
-    <row r="98" spans="1:12">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B98">
-        <v>302.4</v>
+        <v>302.39999999999998</v>
       </c>
       <c r="C98">
         <v>210.8</v>
@@ -4423,22 +4439,22 @@
         <v>2366.81</v>
       </c>
       <c r="E98">
-        <v>2349.55</v>
+        <v>2349.5500000000002</v>
       </c>
       <c r="F98" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G98" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H98" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I98" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J98" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K98">
         <v>1762.85</v>
@@ -4447,9 +4463,9 @@
         <v>1779.14</v>
       </c>
     </row>
-    <row r="99" spans="1:12">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B99">
         <v>4466.2</v>
@@ -4464,19 +4480,19 @@
         <v>2385.89</v>
       </c>
       <c r="F99" t="s">
+        <v>110</v>
+      </c>
+      <c r="G99" t="s">
         <v>112</v>
       </c>
-      <c r="G99" t="s">
-        <v>114</v>
-      </c>
       <c r="H99" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I99" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J99" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K99">
         <v>1765.02</v>
@@ -4485,9 +4501,9 @@
         <v>1795.33</v>
       </c>
     </row>
-    <row r="100" spans="1:12">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B100">
         <v>364.2</v>
@@ -4502,19 +4518,19 @@
         <v>2113.86</v>
       </c>
       <c r="F100" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G100" t="s">
+        <v>114</v>
+      </c>
+      <c r="H100" t="s">
         <v>116</v>
       </c>
-      <c r="H100" t="s">
-        <v>118</v>
-      </c>
       <c r="I100" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J100" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K100">
         <v>1707.02</v>
@@ -4523,9 +4539,9 @@
         <v>1615.48</v>
       </c>
     </row>
-    <row r="101" spans="1:12">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B101">
         <v>1474.7</v>
@@ -4540,19 +4556,19 @@
         <v>2200.75</v>
       </c>
       <c r="F101" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G101" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H101" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I101" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J101" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K101">
         <v>1667.11</v>

--- a/04_Structural_QC/data/structural_wells_100_nonlinear.xlsx
+++ b/04_Structural_QC/data/structural_wells_100_nonlinear.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\My_project\ML_Geophysics\structural_qc_project\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5DC69A-EFFD-44C5-9DAA-32785EB70F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="wells" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="125">
   <si>
     <t>well_id</t>
   </si>
@@ -37,6 +31,12 @@
     <t>Z_map</t>
   </si>
   <si>
+    <t>horizon_id</t>
+  </si>
+  <si>
+    <t>tectonic_zone</t>
+  </si>
+  <si>
     <t>well_category</t>
   </si>
   <si>
@@ -389,19 +389,13 @@
   </si>
   <si>
     <t>oil</t>
-  </si>
-  <si>
-    <t>horizon_id</t>
-  </si>
-  <si>
-    <t>tectonic_zone</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,25 +428,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -490,7 +476,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -524,7 +510,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -559,10 +544,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -735,11 +719,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L101"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L201"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -756,30 +740,30 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>123</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>7501.1</v>
@@ -788,25 +772,25 @@
         <v>9671.5</v>
       </c>
       <c r="D2">
-        <v>2319.0300000000002</v>
+        <v>2319.03</v>
       </c>
       <c r="E2">
-        <v>2324.56</v>
+        <v>2336.71</v>
       </c>
       <c r="F2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K2">
         <v>1713.24</v>
@@ -815,9 +799,9 @@
         <v>1807.63</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>10766.6</v>
@@ -826,25 +810,25 @@
         <v>6577.6</v>
       </c>
       <c r="D3">
-        <v>2485.6799999999998</v>
+        <v>2485.68</v>
       </c>
       <c r="E3">
-        <v>2427.7399999999998</v>
+        <v>2427.74</v>
       </c>
       <c r="F3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K3">
         <v>1768.15</v>
@@ -853,12 +837,12 @@
         <v>1764.18</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4">
-        <v>9308.2000000000007</v>
+        <v>9308.200000000001</v>
       </c>
       <c r="C4">
         <v>4282.2</v>
@@ -870,19 +854,19 @@
         <v>2513.63</v>
       </c>
       <c r="F4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K4">
         <v>1866.42</v>
@@ -891,36 +875,36 @@
         <v>1795.14</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>2702.5</v>
       </c>
       <c r="C5">
-        <v>5237.3999999999996</v>
+        <v>5237.4</v>
       </c>
       <c r="D5">
         <v>2260.54</v>
       </c>
       <c r="E5">
-        <v>2174.61</v>
+        <v>2120.66</v>
       </c>
       <c r="F5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K5">
         <v>1722.59</v>
@@ -929,9 +913,9 @@
         <v>1639.46</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>3602</v>
@@ -940,25 +924,25 @@
         <v>8728.1</v>
       </c>
       <c r="D6">
-        <v>2327.4299999999998</v>
+        <v>2327.43</v>
       </c>
       <c r="E6">
-        <v>2295.79</v>
+        <v>2316.06</v>
       </c>
       <c r="F6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K6">
         <v>1730.67</v>
@@ -967,9 +951,9 @@
         <v>1677.19</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>10482.6</v>
@@ -984,19 +968,19 @@
         <v>2520.35</v>
       </c>
       <c r="F7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K7">
         <v>1860.82</v>
@@ -1005,9 +989,9 @@
         <v>1899.11</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>63.2</v>
@@ -1019,22 +1003,22 @@
         <v>2259.41</v>
       </c>
       <c r="E8">
-        <v>2185.08</v>
+        <v>2180.73</v>
       </c>
       <c r="F8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K8">
         <v>1747.89</v>
@@ -1043,36 +1027,36 @@
         <v>1694.98</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B9">
-        <v>9854.7000000000007</v>
+        <v>9854.700000000001</v>
       </c>
       <c r="C9">
         <v>6836.8</v>
       </c>
       <c r="D9">
-        <v>2485.4899999999998</v>
+        <v>2485.49</v>
       </c>
       <c r="E9">
         <v>2429.08</v>
       </c>
       <c r="F9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K9">
         <v>1851.1</v>
@@ -1081,12 +1065,12 @@
         <v>1817.85</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B10">
-        <v>9564.7999999999993</v>
+        <v>9564.799999999999</v>
       </c>
       <c r="C10">
         <v>3554.1</v>
@@ -1098,19 +1082,19 @@
         <v>2510.41</v>
       </c>
       <c r="F10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K10">
         <v>1869.46</v>
@@ -1119,9 +1103,9 @@
         <v>1890.18</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>5615.2</v>
@@ -1130,25 +1114,25 @@
         <v>5191</v>
       </c>
       <c r="D11">
-        <v>2379.2600000000002</v>
+        <v>2379.26</v>
       </c>
       <c r="E11">
-        <v>2378.1999999999998</v>
+        <v>2380.84</v>
       </c>
       <c r="F11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K11">
         <v>1785.21</v>
@@ -1157,9 +1141,9 @@
         <v>1742.89</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>3636.4</v>
@@ -1171,22 +1155,22 @@
         <v>2297.23</v>
       </c>
       <c r="E12">
-        <v>2238.4</v>
+        <v>2214.28</v>
       </c>
       <c r="F12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K12">
         <v>1699.46</v>
@@ -1195,36 +1179,36 @@
         <v>1639.53</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>3341.1</v>
       </c>
       <c r="C13">
-        <v>9091.7999999999993</v>
+        <v>9091.799999999999</v>
       </c>
       <c r="D13">
         <v>2325.29</v>
       </c>
       <c r="E13">
-        <v>2291.6799999999998</v>
+        <v>2308.63</v>
       </c>
       <c r="F13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K13">
         <v>1763.69</v>
@@ -1233,9 +1217,9 @@
         <v>1733.07</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>3058.4</v>
@@ -1247,22 +1231,22 @@
         <v>2416</v>
       </c>
       <c r="E14">
-        <v>2441.9</v>
+        <v>2502.17</v>
       </c>
       <c r="F14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H14" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K14">
         <v>1742.01</v>
@@ -1271,36 +1255,36 @@
         <v>1811.86</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>5340.9</v>
       </c>
       <c r="C15">
-        <v>9334.2000000000007</v>
+        <v>9334.200000000001</v>
       </c>
       <c r="D15">
         <v>2324.66</v>
       </c>
       <c r="E15">
-        <v>2319.29</v>
+        <v>2308.52</v>
       </c>
       <c r="F15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K15">
         <v>1728.57</v>
@@ -1309,9 +1293,9 @@
         <v>1701.43</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>6054.6</v>
@@ -1323,22 +1307,22 @@
         <v>2474.14</v>
       </c>
       <c r="E16">
-        <v>2499.75</v>
+        <v>2504.13</v>
       </c>
       <c r="F16" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I16" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J16" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K16">
         <v>1805</v>
@@ -1347,9 +1331,9 @@
         <v>1850.8</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>6642</v>
@@ -1358,25 +1342,25 @@
         <v>7529.8</v>
       </c>
       <c r="D17">
-        <v>2362.3200000000002</v>
+        <v>2362.32</v>
       </c>
       <c r="E17">
-        <v>2343.2199999999998</v>
+        <v>2308.89</v>
       </c>
       <c r="F17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I17" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J17" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K17">
         <v>1711.34</v>
@@ -1385,9 +1369,9 @@
         <v>1804.52</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>11946</v>
@@ -1396,25 +1380,25 @@
         <v>8105.3</v>
       </c>
       <c r="D18">
-        <v>2472.9499999999998</v>
+        <v>2472.95</v>
       </c>
       <c r="E18">
-        <v>2415.2800000000002</v>
+        <v>2415.28</v>
       </c>
       <c r="F18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G18" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H18" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I18" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J18" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K18">
         <v>1813.15</v>
@@ -1423,9 +1407,9 @@
         <v>1765.2</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>9511.9</v>
@@ -1440,19 +1424,19 @@
         <v>2448.64</v>
       </c>
       <c r="F19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H19" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K19">
         <v>1877.79</v>
@@ -1461,9 +1445,9 @@
         <v>1810.96</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>7466.2</v>
@@ -1475,22 +1459,22 @@
         <v>2485.79</v>
       </c>
       <c r="E20">
-        <v>2501.31</v>
+        <v>2468.76</v>
       </c>
       <c r="F20" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H20" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I20" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K20">
         <v>1813.67</v>
@@ -1499,9 +1483,9 @@
         <v>1844.18</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>11867.5</v>
@@ -1513,22 +1497,22 @@
         <v>2483.19</v>
       </c>
       <c r="E21">
-        <v>2438.3000000000002</v>
+        <v>2438.3</v>
       </c>
       <c r="F21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H21" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I21" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J21" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K21">
         <v>1789.04</v>
@@ -1537,36 +1521,36 @@
         <v>1816.81</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B22">
-        <v>2583.6999999999998</v>
+        <v>2583.7</v>
       </c>
       <c r="C22">
-        <v>142.69999999999999</v>
+        <v>142.7</v>
       </c>
       <c r="D22">
         <v>2457.11</v>
       </c>
       <c r="E22">
-        <v>2484.59</v>
+        <v>2461.33</v>
       </c>
       <c r="F22" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I22" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K22">
         <v>1805.4</v>
@@ -1575,9 +1559,9 @@
         <v>1861.81</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>1922.5</v>
@@ -1589,22 +1573,22 @@
         <v>2249.67</v>
       </c>
       <c r="E23">
-        <v>2179.88</v>
+        <v>2215.29</v>
       </c>
       <c r="F23" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G23" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H23" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I23" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J23" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K23">
         <v>1719.56</v>
@@ -1613,9 +1597,9 @@
         <v>1680.78</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>7350.5</v>
@@ -1624,25 +1608,25 @@
         <v>7930.2</v>
       </c>
       <c r="D24">
-        <v>2361.4899999999998</v>
+        <v>2361.49</v>
       </c>
       <c r="E24">
-        <v>2374.5700000000002</v>
+        <v>2412.05</v>
       </c>
       <c r="F24" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G24" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H24" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I24" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K24">
         <v>1762.46</v>
@@ -1651,12 +1635,12 @@
         <v>1818.49</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B25">
-        <v>527.29999999999995</v>
+        <v>527.3</v>
       </c>
       <c r="C25">
         <v>5130</v>
@@ -1665,22 +1649,22 @@
         <v>2260.5</v>
       </c>
       <c r="E25">
-        <v>2190.77</v>
+        <v>2202.73</v>
       </c>
       <c r="F25" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G25" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H25" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I25" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K25">
         <v>1702.52</v>
@@ -1689,9 +1673,9 @@
         <v>1632.66</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>428.2</v>
@@ -1703,22 +1687,22 @@
         <v>2232.21</v>
       </c>
       <c r="E26">
-        <v>2149.38</v>
+        <v>2170.01</v>
       </c>
       <c r="F26" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G26" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H26" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I26" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J26" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K26">
         <v>1649.23</v>
@@ -1727,36 +1711,36 @@
         <v>1622.58</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>6178.7</v>
       </c>
       <c r="C27">
-        <v>2264.1999999999998</v>
+        <v>2264.2</v>
       </c>
       <c r="D27">
         <v>2433.75</v>
       </c>
       <c r="E27">
-        <v>2460.33</v>
+        <v>2513.53</v>
       </c>
       <c r="F27" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H27" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I27" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J27" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K27">
         <v>1809.04</v>
@@ -1765,9 +1749,9 @@
         <v>1841.29</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>5594.5</v>
@@ -1776,25 +1760,25 @@
         <v>1985.2</v>
       </c>
       <c r="D28">
-        <v>2443.4499999999998</v>
+        <v>2443.45</v>
       </c>
       <c r="E28">
-        <v>2454.2600000000002</v>
+        <v>2458.24</v>
       </c>
       <c r="F28" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H28" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J28" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K28">
         <v>1813.72</v>
@@ -1803,9 +1787,9 @@
         <v>1789.21</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>11006</v>
@@ -1820,19 +1804,19 @@
         <v>2502</v>
       </c>
       <c r="F29" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G29" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I29" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J29" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K29">
         <v>1885.5</v>
@@ -1841,9 +1825,9 @@
         <v>1809.5</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>7550.7</v>
@@ -1852,25 +1836,25 @@
         <v>1794.1</v>
       </c>
       <c r="D30">
-        <v>2467.4899999999998</v>
+        <v>2467.49</v>
       </c>
       <c r="E30">
-        <v>2470.0700000000002</v>
+        <v>2435.84</v>
       </c>
       <c r="F30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H30" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I30" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J30" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K30">
         <v>1853.22</v>
@@ -1879,9 +1863,9 @@
         <v>1812.85</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>6169.4</v>
@@ -1893,22 +1877,22 @@
         <v>2430.09</v>
       </c>
       <c r="E31">
-        <v>2438.2600000000002</v>
+        <v>2445.46</v>
       </c>
       <c r="F31" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G31" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H31" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I31" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K31">
         <v>1812.14</v>
@@ -1917,36 +1901,36 @@
         <v>1811.62</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>5962.5</v>
       </c>
       <c r="C32">
-        <v>9481.2000000000007</v>
+        <v>9481.200000000001</v>
       </c>
       <c r="D32">
         <v>2314.11</v>
       </c>
       <c r="E32">
-        <v>2336.69</v>
+        <v>2390.38</v>
       </c>
       <c r="F32" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H32" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J32" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K32">
         <v>1687.72</v>
@@ -1955,9 +1939,9 @@
         <v>1724.68</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>2970.2</v>
@@ -1966,25 +1950,25 @@
         <v>5733.3</v>
       </c>
       <c r="D33">
-        <v>2265.0500000000002</v>
+        <v>2265.05</v>
       </c>
       <c r="E33">
-        <v>2193.66</v>
+        <v>2188.92</v>
       </c>
       <c r="F33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K33">
         <v>1666.57</v>
@@ -1993,9 +1977,9 @@
         <v>1688.65</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>141.5</v>
@@ -2004,25 +1988,25 @@
         <v>3400.7</v>
       </c>
       <c r="D34">
-        <v>2288.2199999999998</v>
+        <v>2288.22</v>
       </c>
       <c r="E34">
-        <v>2224.9299999999998</v>
+        <v>2202.4</v>
       </c>
       <c r="F34" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G34" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H34" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I34" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J34" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K34">
         <v>1688.28</v>
@@ -2031,12 +2015,12 @@
         <v>1736.79</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B35">
-        <v>2308.8000000000002</v>
+        <v>2308.8</v>
       </c>
       <c r="C35">
         <v>2715.2</v>
@@ -2045,22 +2029,22 @@
         <v>2350.08</v>
       </c>
       <c r="E35">
-        <v>2311.5500000000002</v>
+        <v>2254.27</v>
       </c>
       <c r="F35" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G35" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H35" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I35" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J35" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K35">
         <v>1759.07</v>
@@ -2069,9 +2053,9 @@
         <v>1661.25</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>8304.4</v>
@@ -2086,19 +2070,19 @@
         <v>2362.9</v>
       </c>
       <c r="F36" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G36" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H36" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I36" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J36" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K36">
         <v>1714.47</v>
@@ -2107,12 +2091,12 @@
         <v>1669.41</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B37">
-        <v>2407.3000000000002</v>
+        <v>2407.3</v>
       </c>
       <c r="C37">
         <v>4444.8</v>
@@ -2121,22 +2105,22 @@
         <v>2282.33</v>
       </c>
       <c r="E37">
-        <v>2224.52</v>
+        <v>2237.15</v>
       </c>
       <c r="F37" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G37" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H37" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I37" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J37" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K37">
         <v>1749.66</v>
@@ -2145,12 +2129,12 @@
         <v>1711.97</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B38">
-        <v>4434.3999999999996</v>
+        <v>4434.4</v>
       </c>
       <c r="C38">
         <v>9803.9</v>
@@ -2159,22 +2143,22 @@
         <v>2325.15</v>
       </c>
       <c r="E38">
-        <v>2329.12</v>
+        <v>2339.14</v>
       </c>
       <c r="F38" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G38" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H38" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I38" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J38" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K38">
         <v>1744.29</v>
@@ -2183,9 +2167,9 @@
         <v>1709.03</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>44.8</v>
@@ -2197,22 +2181,22 @@
         <v>2279.31</v>
       </c>
       <c r="E39">
-        <v>2219.35</v>
+        <v>2229.85</v>
       </c>
       <c r="F39" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G39" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H39" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I39" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J39" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K39">
         <v>1722.67</v>
@@ -2221,9 +2205,9 @@
         <v>1736.36</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B40">
         <v>9960.6</v>
@@ -2232,25 +2216,25 @@
         <v>5211.7</v>
       </c>
       <c r="D40">
-        <v>2511.2199999999998</v>
+        <v>2511.22</v>
       </c>
       <c r="E40">
-        <v>2463.7399999999998</v>
+        <v>2463.74</v>
       </c>
       <c r="F40" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G40" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H40" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I40" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J40" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K40">
         <v>1856.1</v>
@@ -2259,9 +2243,9 @@
         <v>1922.5</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B41">
         <v>1853.5</v>
@@ -2273,22 +2257,22 @@
         <v>2288.21</v>
       </c>
       <c r="E41">
-        <v>2220.42</v>
+        <v>2179.63</v>
       </c>
       <c r="F41" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G41" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H41" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I41" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J41" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K41">
         <v>1726.86</v>
@@ -2297,9 +2281,9 @@
         <v>1675.03</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B42">
         <v>3211.2</v>
@@ -2311,22 +2295,22 @@
         <v>2295.41</v>
       </c>
       <c r="E42">
-        <v>2233.29</v>
+        <v>2199.78</v>
       </c>
       <c r="F42" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G42" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H42" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I42" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J42" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K42">
         <v>1683.8</v>
@@ -2335,9 +2319,9 @@
         <v>1672.77</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B43">
         <v>10564</v>
@@ -2346,25 +2330,25 @@
         <v>5806.5</v>
       </c>
       <c r="D43">
-        <v>2506.9699999999998</v>
+        <v>2506.97</v>
       </c>
       <c r="E43">
-        <v>2457.5300000000002</v>
+        <v>2457.53</v>
       </c>
       <c r="F43" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G43" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H43" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I43" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J43" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K43">
         <v>1899.55</v>
@@ -2373,9 +2357,9 @@
         <v>1807.8</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B44">
         <v>6117.5</v>
@@ -2387,22 +2371,22 @@
         <v>2416.6</v>
       </c>
       <c r="E44">
-        <v>2410.86</v>
+        <v>2394.49</v>
       </c>
       <c r="F44" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G44" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H44" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I44" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J44" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K44">
         <v>1825.81</v>
@@ -2411,12 +2395,12 @@
         <v>1794.44</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B45">
-        <v>10165.799999999999</v>
+        <v>10165.8</v>
       </c>
       <c r="C45">
         <v>8781.9</v>
@@ -2425,22 +2409,22 @@
         <v>2405.04</v>
       </c>
       <c r="E45">
-        <v>2398.8200000000002</v>
+        <v>2398.82</v>
       </c>
       <c r="F45" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G45" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H45" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I45" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J45" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K45">
         <v>1821.31</v>
@@ -2449,9 +2433,9 @@
         <v>1775.39</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B46">
         <v>7676.6</v>
@@ -2463,22 +2447,22 @@
         <v>2498</v>
       </c>
       <c r="E46">
-        <v>2557.5500000000002</v>
+        <v>2602.27</v>
       </c>
       <c r="F46" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G46" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H46" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I46" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J46" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K46">
         <v>1809.07</v>
@@ -2487,12 +2471,12 @@
         <v>1824.73</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B47">
-        <v>8901.2999999999993</v>
+        <v>8901.299999999999</v>
       </c>
       <c r="C47">
         <v>9227.6</v>
@@ -2504,19 +2488,19 @@
         <v>2380.16</v>
       </c>
       <c r="F47" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G47" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H47" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I47" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J47" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K47">
         <v>1701.05</v>
@@ -2525,12 +2509,12 @@
         <v>1783.29</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B48">
-        <v>1097.9000000000001</v>
+        <v>1097.9</v>
       </c>
       <c r="C48">
         <v>687.2</v>
@@ -2539,22 +2523,22 @@
         <v>2390.37</v>
       </c>
       <c r="E48">
-        <v>2388.8200000000002</v>
+        <v>2393.64</v>
       </c>
       <c r="F48" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G48" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H48" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I48" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J48" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K48">
         <v>1732.24</v>
@@ -2563,9 +2547,9 @@
         <v>1693.6</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B49">
         <v>6493.7</v>
@@ -2574,25 +2558,25 @@
         <v>4300</v>
       </c>
       <c r="D49">
-        <v>2442.2399999999998</v>
+        <v>2442.24</v>
       </c>
       <c r="E49">
-        <v>2439.17</v>
+        <v>2414.88</v>
       </c>
       <c r="F49" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G49" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H49" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I49" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J49" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K49">
         <v>1771.79</v>
@@ -2601,36 +2585,36 @@
         <v>1813.69</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B50">
         <v>6093.3</v>
       </c>
       <c r="C50">
-        <v>5195.1000000000004</v>
+        <v>5195.1</v>
       </c>
       <c r="D50">
-        <v>2420.1999999999998</v>
+        <v>2420.2</v>
       </c>
       <c r="E50">
-        <v>2428.61</v>
+        <v>2441.8</v>
       </c>
       <c r="F50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G50" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H50" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I50" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J50" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K50">
         <v>1812.13</v>
@@ -2639,9 +2623,9 @@
         <v>1796.79</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B51">
         <v>10456.1</v>
@@ -2650,25 +2634,25 @@
         <v>9509.4</v>
       </c>
       <c r="D51">
-        <v>2402.0500000000002</v>
+        <v>2402.05</v>
       </c>
       <c r="E51">
         <v>2383.61</v>
       </c>
       <c r="F51" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G51" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H51" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I51" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J51" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K51">
         <v>1803.02</v>
@@ -2677,9 +2661,9 @@
         <v>1819.77</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B52">
         <v>4335.2</v>
@@ -2691,22 +2675,22 @@
         <v>2387.89</v>
       </c>
       <c r="E52">
-        <v>2365.62</v>
+        <v>2323.96</v>
       </c>
       <c r="F52" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G52" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H52" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I52" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J52" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K52">
         <v>1810.48</v>
@@ -2715,9 +2699,9 @@
         <v>1765.81</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B53">
         <v>7178.2</v>
@@ -2729,22 +2713,22 @@
         <v>2358.94</v>
       </c>
       <c r="E53">
-        <v>2366.1999999999998</v>
+        <v>2388.85</v>
       </c>
       <c r="F53" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H53" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I53" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J53" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K53">
         <v>1813.39</v>
@@ -2753,9 +2737,9 @@
         <v>1778.6</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B54">
         <v>711</v>
@@ -2767,22 +2751,22 @@
         <v>2231.77</v>
       </c>
       <c r="E54">
-        <v>2149.7600000000002</v>
+        <v>2174.69</v>
       </c>
       <c r="F54" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G54" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H54" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I54" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J54" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K54">
         <v>1700.77</v>
@@ -2791,12 +2775,12 @@
         <v>1604.42</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B55">
-        <v>4651.6000000000004</v>
+        <v>4651.6</v>
       </c>
       <c r="C55">
         <v>7170.9</v>
@@ -2805,22 +2789,22 @@
         <v>2306.19</v>
       </c>
       <c r="E55">
-        <v>2317.02</v>
+        <v>2337.92</v>
       </c>
       <c r="F55" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G55" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H55" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I55" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J55" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K55">
         <v>1737.01</v>
@@ -2829,9 +2813,9 @@
         <v>1740.12</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B56">
         <v>3876.4</v>
@@ -2843,22 +2827,22 @@
         <v>2296.63</v>
       </c>
       <c r="E56">
-        <v>2223.4699999999998</v>
+        <v>2142.44</v>
       </c>
       <c r="F56" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G56" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H56" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I56" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J56" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K56">
         <v>1712.57</v>
@@ -2867,9 +2851,9 @@
         <v>1712.32</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B57">
         <v>1802.4</v>
@@ -2881,22 +2865,22 @@
         <v>2286.83</v>
       </c>
       <c r="E57">
-        <v>2226.79</v>
+        <v>2220.51</v>
       </c>
       <c r="F57" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G57" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H57" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I57" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J57" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K57">
         <v>1707.95</v>
@@ -2905,9 +2889,9 @@
         <v>1723.61</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B58">
         <v>9796.1</v>
@@ -2916,25 +2900,25 @@
         <v>3326.8</v>
       </c>
       <c r="D58">
-        <v>2530.5700000000002</v>
+        <v>2530.57</v>
       </c>
       <c r="E58">
-        <v>2488.4299999999998</v>
+        <v>2488.43</v>
       </c>
       <c r="F58" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G58" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H58" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I58" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J58" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K58">
         <v>1814.87</v>
@@ -2943,12 +2927,12 @@
         <v>1828.76</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B59">
-        <v>4553.3999999999996</v>
+        <v>4553.4</v>
       </c>
       <c r="C59">
         <v>3982.8</v>
@@ -2957,22 +2941,22 @@
         <v>2351.13</v>
       </c>
       <c r="E59">
-        <v>2357.29</v>
+        <v>2376.73</v>
       </c>
       <c r="F59" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G59" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H59" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I59" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J59" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K59">
         <v>1765.43</v>
@@ -2981,9 +2965,9 @@
         <v>1816.46</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B60">
         <v>11745</v>
@@ -2992,25 +2976,25 @@
         <v>2029.1</v>
       </c>
       <c r="D60">
-        <v>2571.2600000000002</v>
+        <v>2571.26</v>
       </c>
       <c r="E60">
         <v>2599.81</v>
       </c>
       <c r="F60" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G60" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H60" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I60" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J60" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K60">
         <v>1875.28</v>
@@ -3019,9 +3003,9 @@
         <v>1930.66</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B61">
         <v>7079.9</v>
@@ -3033,22 +3017,22 @@
         <v>2466.37</v>
       </c>
       <c r="E61">
-        <v>2491.4899999999998</v>
+        <v>2505.47</v>
       </c>
       <c r="F61" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G61" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H61" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I61" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J61" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K61">
         <v>1801.81</v>
@@ -3057,9 +3041,9 @@
         <v>1800.49</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B62">
         <v>7260.7</v>
@@ -3071,22 +3055,22 @@
         <v>2464.59</v>
       </c>
       <c r="E62">
-        <v>2479.81</v>
+        <v>2473.44</v>
       </c>
       <c r="F62" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G62" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H62" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I62" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J62" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K62">
         <v>1790.01</v>
@@ -3095,9 +3079,9 @@
         <v>1724.06</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B63">
         <v>7656</v>
@@ -3109,22 +3093,22 @@
         <v>2328.56</v>
       </c>
       <c r="E63">
-        <v>2322.91</v>
+        <v>2312.34</v>
       </c>
       <c r="F63" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G63" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H63" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I63" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J63" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K63">
         <v>1751.85</v>
@@ -3133,36 +3117,36 @@
         <v>1694.01</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B64">
         <v>8117.4</v>
       </c>
       <c r="C64">
-        <v>8401.7000000000007</v>
+        <v>8401.700000000001</v>
       </c>
       <c r="D64">
         <v>2364.14</v>
       </c>
       <c r="E64">
-        <v>2362.8200000000002</v>
+        <v>2365.53</v>
       </c>
       <c r="F64" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G64" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H64" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K64">
         <v>1793.73</v>
@@ -3171,36 +3155,36 @@
         <v>1760.63</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B65">
         <v>1809.5</v>
       </c>
       <c r="C65">
-        <v>1124.0999999999999</v>
+        <v>1124.1</v>
       </c>
       <c r="D65">
-        <v>2405.5300000000002</v>
+        <v>2405.53</v>
       </c>
       <c r="E65">
-        <v>2401.4699999999998</v>
+        <v>2369.08</v>
       </c>
       <c r="F65" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G65" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H65" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I65" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J65" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K65">
         <v>1782.89</v>
@@ -3209,9 +3193,9 @@
         <v>1784.73</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B66">
         <v>5283.8</v>
@@ -3223,22 +3207,22 @@
         <v>2364.19</v>
       </c>
       <c r="E66">
-        <v>2353.0100000000002</v>
+        <v>2334.54</v>
       </c>
       <c r="F66" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G66" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H66" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I66" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J66" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K66">
         <v>1766.33</v>
@@ -3247,9 +3231,9 @@
         <v>1741.36</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B67">
         <v>2874.8</v>
@@ -3258,25 +3242,25 @@
         <v>4792</v>
       </c>
       <c r="D67">
-        <v>2284.0500000000002</v>
+        <v>2284.05</v>
       </c>
       <c r="E67">
-        <v>2216.94</v>
+        <v>2188.02</v>
       </c>
       <c r="F67" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G67" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H67" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I67" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J67" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K67">
         <v>1700.76</v>
@@ -3285,9 +3269,9 @@
         <v>1662.32</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B68">
         <v>4830</v>
@@ -3296,25 +3280,25 @@
         <v>5946.8</v>
       </c>
       <c r="D68">
-        <v>2340.1999999999998</v>
+        <v>2340.2</v>
       </c>
       <c r="E68">
-        <v>2332.0700000000002</v>
+        <v>2318.18</v>
       </c>
       <c r="F68" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G68" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H68" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I68" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J68" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K68">
         <v>1739.19</v>
@@ -3323,36 +3307,36 @@
         <v>1766.64</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B69">
-        <v>1160.4000000000001</v>
+        <v>1160.4</v>
       </c>
       <c r="C69">
         <v>6592.8</v>
       </c>
       <c r="D69">
-        <v>2242.3000000000002</v>
+        <v>2242.3</v>
       </c>
       <c r="E69">
-        <v>2168.79</v>
+        <v>2205.21</v>
       </c>
       <c r="F69" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G69" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H69" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I69" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J69" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K69">
         <v>1684.11</v>
@@ -3361,9 +3345,9 @@
         <v>1628.98</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B70">
         <v>11613.9</v>
@@ -3378,19 +3362,19 @@
         <v>2549.62</v>
       </c>
       <c r="F70" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G70" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H70" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I70" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J70" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K70">
         <v>1850.74</v>
@@ -3399,9 +3383,9 @@
         <v>1773.27</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B71">
         <v>2580</v>
@@ -3413,22 +3397,22 @@
         <v>2298.59</v>
       </c>
       <c r="E71">
-        <v>2255.0500000000002</v>
+        <v>2290.08</v>
       </c>
       <c r="F71" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G71" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H71" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I71" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J71" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K71">
         <v>1707.35</v>
@@ -3437,36 +3421,36 @@
         <v>1687.58</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B72">
         <v>8061.2</v>
       </c>
       <c r="C72">
-        <v>4658.3999999999996</v>
+        <v>4658.4</v>
       </c>
       <c r="D72">
         <v>2510.56</v>
       </c>
       <c r="E72">
-        <v>2558.36</v>
+        <v>2536.57</v>
       </c>
       <c r="F72" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G72" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H72" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I72" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J72" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K72">
         <v>1846.26</v>
@@ -3475,9 +3459,9 @@
         <v>1899.62</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B73">
         <v>3605</v>
@@ -3486,25 +3470,25 @@
         <v>6281</v>
       </c>
       <c r="D73">
-        <v>2282.5500000000002</v>
+        <v>2282.55</v>
       </c>
       <c r="E73">
-        <v>2226.42</v>
+        <v>2245.39</v>
       </c>
       <c r="F73" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G73" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H73" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I73" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J73" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K73">
         <v>1749.52</v>
@@ -3513,9 +3497,9 @@
         <v>1650.87</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B74">
         <v>10488.9</v>
@@ -3524,25 +3508,25 @@
         <v>6352.3</v>
       </c>
       <c r="D74">
-        <v>2492.5300000000002</v>
+        <v>2492.53</v>
       </c>
       <c r="E74">
         <v>2429.75</v>
       </c>
       <c r="F74" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G74" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H74" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I74" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K74">
         <v>1800.88</v>
@@ -3551,9 +3535,9 @@
         <v>1818.28</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B75">
         <v>7946.6</v>
@@ -3565,22 +3549,22 @@
         <v>2471.84</v>
       </c>
       <c r="E75">
-        <v>2494.4699999999998</v>
+        <v>2495.33</v>
       </c>
       <c r="F75" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G75" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H75" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I75" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J75" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K75">
         <v>1853.08</v>
@@ -3589,36 +3573,36 @@
         <v>1849.59</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B76">
         <v>1579.4</v>
       </c>
       <c r="C76">
-        <v>618.70000000000005</v>
+        <v>618.7</v>
       </c>
       <c r="D76">
         <v>2402.75</v>
       </c>
       <c r="E76">
-        <v>2405.0700000000002</v>
+        <v>2398.52</v>
       </c>
       <c r="F76" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G76" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H76" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I76" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J76" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K76">
         <v>1768.42</v>
@@ -3627,9 +3611,9 @@
         <v>1779.83</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B77">
         <v>10140.9</v>
@@ -3638,25 +3622,25 @@
         <v>4115.2</v>
       </c>
       <c r="D77">
-        <v>2545.3200000000002</v>
+        <v>2545.32</v>
       </c>
       <c r="E77">
         <v>2513.71</v>
       </c>
       <c r="F77" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G77" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H77" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I77" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J77" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K77">
         <v>1843.65</v>
@@ -3665,9 +3649,9 @@
         <v>1853.09</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B78">
         <v>11339.4</v>
@@ -3682,19 +3666,19 @@
         <v>2424.04</v>
       </c>
       <c r="F78" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G78" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H78" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I78" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J78" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K78">
         <v>1764.78</v>
@@ -3703,9 +3687,9 @@
         <v>1754.93</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B79">
         <v>10847</v>
@@ -3720,19 +3704,19 @@
         <v>2412.59</v>
       </c>
       <c r="F79" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G79" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H79" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I79" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J79" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K79">
         <v>1737.97</v>
@@ -3741,9 +3725,9 @@
         <v>1786.78</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B80">
         <v>6836.6</v>
@@ -3755,22 +3739,22 @@
         <v>2392.02</v>
       </c>
       <c r="E80">
-        <v>2390.09</v>
+        <v>2388.96</v>
       </c>
       <c r="F80" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G80" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H80" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I80" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J80" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K80">
         <v>1793.28</v>
@@ -3779,9 +3763,9 @@
         <v>1830.65</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B81">
         <v>1745.5</v>
@@ -3793,22 +3777,22 @@
         <v>2405.41</v>
       </c>
       <c r="E81">
-        <v>2413.04</v>
+        <v>2422.25</v>
       </c>
       <c r="F81" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G81" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H81" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I81" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J81" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K81">
         <v>1751.37</v>
@@ -3817,9 +3801,9 @@
         <v>1781.73</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B82">
         <v>2309.6</v>
@@ -3831,22 +3815,22 @@
         <v>2278.65</v>
       </c>
       <c r="E82">
-        <v>2223.83</v>
+        <v>2256.66</v>
       </c>
       <c r="F82" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G82" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H82" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I82" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J82" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K82">
         <v>1734.13</v>
@@ -3855,9 +3839,9 @@
         <v>1639.69</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B83">
         <v>11134.9</v>
@@ -3866,25 +3850,25 @@
         <v>8020.4</v>
       </c>
       <c r="D83">
-        <v>2464.8200000000002</v>
+        <v>2464.82</v>
       </c>
       <c r="E83">
-        <v>2406.4499999999998</v>
+        <v>2406.45</v>
       </c>
       <c r="F83" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G83" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H83" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I83" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J83" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K83">
         <v>1813.23</v>
@@ -3893,9 +3877,9 @@
         <v>1837.91</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B84">
         <v>6627.9</v>
@@ -3907,22 +3891,22 @@
         <v>2333.19</v>
       </c>
       <c r="E84">
-        <v>2320.86</v>
+        <v>2297.21</v>
       </c>
       <c r="F84" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G84" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H84" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I84" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J84" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K84">
         <v>1748.8</v>
@@ -3931,9 +3915,9 @@
         <v>1682.68</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B85">
         <v>2166.6</v>
@@ -3945,22 +3929,22 @@
         <v>2261.61</v>
       </c>
       <c r="E85">
-        <v>2191.88</v>
+        <v>2201.41</v>
       </c>
       <c r="F85" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G85" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H85" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I85" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J85" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K85">
         <v>1738.97</v>
@@ -3969,9 +3953,9 @@
         <v>1728.7</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B86">
         <v>10608.7</v>
@@ -3983,22 +3967,22 @@
         <v>2409.66</v>
       </c>
       <c r="E86">
-        <v>2398.9899999999998</v>
+        <v>2398.99</v>
       </c>
       <c r="F86" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G86" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H86" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I86" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J86" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K86">
         <v>1780.95</v>
@@ -4007,9 +3991,9 @@
         <v>1780.93</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B87">
         <v>7698.9</v>
@@ -4018,25 +4002,25 @@
         <v>466.5</v>
       </c>
       <c r="D87">
-        <v>2460.2600000000002</v>
+        <v>2460.26</v>
       </c>
       <c r="E87">
-        <v>2476.91</v>
+        <v>2478.44</v>
       </c>
       <c r="F87" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G87" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H87" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I87" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J87" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K87">
         <v>1721.86</v>
@@ -4045,36 +4029,36 @@
         <v>1842.13</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B88">
         <v>6836.3</v>
       </c>
       <c r="C88">
-        <v>302.89999999999998</v>
+        <v>302.9</v>
       </c>
       <c r="D88">
         <v>2459.34</v>
       </c>
       <c r="E88">
-        <v>2488.1999999999998</v>
+        <v>2521.09</v>
       </c>
       <c r="F88" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G88" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H88" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I88" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J88" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K88">
         <v>1762.36</v>
@@ -4083,9 +4067,9 @@
         <v>1837.76</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B89">
         <v>4515.5</v>
@@ -4094,25 +4078,25 @@
         <v>202.2</v>
       </c>
       <c r="D89">
-        <v>2484.6999999999998</v>
+        <v>2484.7</v>
       </c>
       <c r="E89">
-        <v>2511.39</v>
+        <v>2501.91</v>
       </c>
       <c r="F89" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G89" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H89" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I89" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J89" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K89">
         <v>1848.32</v>
@@ -4121,36 +4105,36 @@
         <v>1836.84</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B90">
         <v>4931.5</v>
       </c>
       <c r="C90">
-        <v>2527.6999999999998</v>
+        <v>2527.7</v>
       </c>
       <c r="D90">
-        <v>2418.1999999999998</v>
+        <v>2418.2</v>
       </c>
       <c r="E90">
-        <v>2411.6799999999998</v>
+        <v>2393.08</v>
       </c>
       <c r="F90" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G90" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H90" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I90" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J90" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K90">
         <v>1840.97</v>
@@ -4159,36 +4143,36 @@
         <v>1825.75</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B91">
         <v>2873.9</v>
       </c>
       <c r="C91">
-        <v>2485.6999999999998</v>
+        <v>2485.7</v>
       </c>
       <c r="D91">
         <v>2372.36</v>
       </c>
       <c r="E91">
-        <v>2354.25</v>
+        <v>2331.19</v>
       </c>
       <c r="F91" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G91" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H91" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I91" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J91" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K91">
         <v>1760.5</v>
@@ -4197,9 +4181,9 @@
         <v>1750.41</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B92">
         <v>456.7</v>
@@ -4211,22 +4195,22 @@
         <v>2344.11</v>
       </c>
       <c r="E92">
-        <v>2323.0100000000002</v>
+        <v>2349.61</v>
       </c>
       <c r="F92" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G92" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H92" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I92" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J92" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K92">
         <v>1729.12</v>
@@ -4235,9 +4219,9 @@
         <v>1704.92</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B93">
         <v>10514.6</v>
@@ -4249,22 +4233,22 @@
         <v>2506.34</v>
       </c>
       <c r="E93">
-        <v>2458.2600000000002</v>
+        <v>2458.26</v>
       </c>
       <c r="F93" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G93" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H93" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I93" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J93" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K93">
         <v>1796.09</v>
@@ -4273,9 +4257,9 @@
         <v>1810.18</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B94">
         <v>5612.8</v>
@@ -4287,22 +4271,22 @@
         <v>2463.77</v>
       </c>
       <c r="E94">
-        <v>2468.48</v>
+        <v>2441.86</v>
       </c>
       <c r="F94" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G94" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H94" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I94" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J94" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K94">
         <v>1825.98</v>
@@ -4311,9 +4295,9 @@
         <v>1746.17</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B95">
         <v>6571.6</v>
@@ -4322,25 +4306,25 @@
         <v>5903.9</v>
       </c>
       <c r="D95">
-        <v>2408.2800000000002</v>
+        <v>2408.28</v>
       </c>
       <c r="E95">
-        <v>2422.61</v>
+        <v>2455.91</v>
       </c>
       <c r="F95" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G95" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H95" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I95" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J95" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K95">
         <v>1733.92</v>
@@ -4349,9 +4333,9 @@
         <v>1784.18</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B96">
         <v>3866</v>
@@ -4363,22 +4347,22 @@
         <v>2440.9</v>
       </c>
       <c r="E96">
-        <v>2470.23</v>
+        <v>2489.95</v>
       </c>
       <c r="F96" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G96" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H96" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I96" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J96" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K96">
         <v>1765.93</v>
@@ -4387,9 +4371,9 @@
         <v>1746.04</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B97">
         <v>9015.9</v>
@@ -4404,19 +4388,19 @@
         <v>2427.46</v>
       </c>
       <c r="F97" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G97" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H97" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I97" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J97" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K97">
         <v>1817.56</v>
@@ -4425,12 +4409,12 @@
         <v>1793.23</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B98">
-        <v>302.39999999999998</v>
+        <v>302.4</v>
       </c>
       <c r="C98">
         <v>210.8</v>
@@ -4439,22 +4423,22 @@
         <v>2366.81</v>
       </c>
       <c r="E98">
-        <v>2349.5500000000002</v>
+        <v>2342.09</v>
       </c>
       <c r="F98" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G98" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H98" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I98" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J98" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K98">
         <v>1762.85</v>
@@ -4463,9 +4447,9 @@
         <v>1779.14</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B99">
         <v>4466.2</v>
@@ -4477,22 +4461,22 @@
         <v>2389.04</v>
       </c>
       <c r="E99">
-        <v>2385.89</v>
+        <v>2382.61</v>
       </c>
       <c r="F99" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G99" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H99" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I99" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J99" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K99">
         <v>1765.02</v>
@@ -4501,9 +4485,9 @@
         <v>1795.33</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B100">
         <v>364.2</v>
@@ -4515,22 +4499,22 @@
         <v>2216.75</v>
       </c>
       <c r="E100">
-        <v>2113.86</v>
+        <v>2086.82</v>
       </c>
       <c r="F100" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G100" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H100" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I100" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J100" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K100">
         <v>1707.02</v>
@@ -4539,9 +4523,9 @@
         <v>1615.48</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B101">
         <v>1474.7</v>
@@ -4553,28 +4537,3828 @@
         <v>2256.62</v>
       </c>
       <c r="E101">
-        <v>2200.75</v>
+        <v>2277.51</v>
       </c>
       <c r="F101" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G101" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H101" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I101" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J101" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K101">
         <v>1667.11</v>
       </c>
       <c r="L101">
         <v>1565.23</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" t="s">
+        <v>12</v>
+      </c>
+      <c r="B102">
+        <v>7501.1</v>
+      </c>
+      <c r="C102">
+        <v>9671.5</v>
+      </c>
+      <c r="D102">
+        <v>2248.07</v>
+      </c>
+      <c r="E102">
+        <v>2286.52</v>
+      </c>
+      <c r="F102" t="s">
+        <v>113</v>
+      </c>
+      <c r="G102" t="s">
+        <v>114</v>
+      </c>
+      <c r="H102" t="s">
+        <v>117</v>
+      </c>
+      <c r="I102" t="s">
+        <v>120</v>
+      </c>
+      <c r="J102" t="s">
+        <v>120</v>
+      </c>
+      <c r="K102">
+        <v>1660.82</v>
+      </c>
+      <c r="L102">
+        <v>1758.21</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103" t="s">
+        <v>13</v>
+      </c>
+      <c r="B103">
+        <v>10766.6</v>
+      </c>
+      <c r="C103">
+        <v>6577.6</v>
+      </c>
+      <c r="D103">
+        <v>2443.25</v>
+      </c>
+      <c r="E103">
+        <v>2408.21</v>
+      </c>
+      <c r="F103" t="s">
+        <v>113</v>
+      </c>
+      <c r="G103" t="s">
+        <v>115</v>
+      </c>
+      <c r="H103" t="s">
+        <v>117</v>
+      </c>
+      <c r="I103" t="s">
+        <v>121</v>
+      </c>
+      <c r="J103" t="s">
+        <v>122</v>
+      </c>
+      <c r="K103">
+        <v>1737.97</v>
+      </c>
+      <c r="L103">
+        <v>1728.79</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12">
+      <c r="A104" t="s">
+        <v>14</v>
+      </c>
+      <c r="B104">
+        <v>9308.200000000001</v>
+      </c>
+      <c r="C104">
+        <v>4282.2</v>
+      </c>
+      <c r="D104">
+        <v>2494.91</v>
+      </c>
+      <c r="E104">
+        <v>2441.8</v>
+      </c>
+      <c r="F104" t="s">
+        <v>113</v>
+      </c>
+      <c r="G104" t="s">
+        <v>115</v>
+      </c>
+      <c r="H104" t="s">
+        <v>117</v>
+      </c>
+      <c r="I104" t="s">
+        <v>121</v>
+      </c>
+      <c r="J104" t="s">
+        <v>122</v>
+      </c>
+      <c r="K104">
+        <v>1834.05</v>
+      </c>
+      <c r="L104">
+        <v>1762.71</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105">
+        <v>2702.5</v>
+      </c>
+      <c r="C105">
+        <v>5237.4</v>
+      </c>
+      <c r="D105">
+        <v>2304.05</v>
+      </c>
+      <c r="E105">
+        <v>2160.21</v>
+      </c>
+      <c r="F105" t="s">
+        <v>112</v>
+      </c>
+      <c r="G105" t="s">
+        <v>116</v>
+      </c>
+      <c r="H105" t="s">
+        <v>117</v>
+      </c>
+      <c r="I105" t="s">
+        <v>120</v>
+      </c>
+      <c r="J105" t="s">
+        <v>120</v>
+      </c>
+      <c r="K105">
+        <v>1755.75</v>
+      </c>
+      <c r="L105">
+        <v>1675.73</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12">
+      <c r="A106" t="s">
+        <v>16</v>
+      </c>
+      <c r="B106">
+        <v>3602</v>
+      </c>
+      <c r="C106">
+        <v>8728.1</v>
+      </c>
+      <c r="D106">
+        <v>2278.11</v>
+      </c>
+      <c r="E106">
+        <v>2205.1</v>
+      </c>
+      <c r="F106" t="s">
+        <v>113</v>
+      </c>
+      <c r="G106" t="s">
+        <v>116</v>
+      </c>
+      <c r="H106" t="s">
+        <v>118</v>
+      </c>
+      <c r="I106" t="s">
+        <v>120</v>
+      </c>
+      <c r="J106" t="s">
+        <v>120</v>
+      </c>
+      <c r="K106">
+        <v>1694</v>
+      </c>
+      <c r="L106">
+        <v>1642.39</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12">
+      <c r="A107" t="s">
+        <v>17</v>
+      </c>
+      <c r="B107">
+        <v>10482.6</v>
+      </c>
+      <c r="C107">
+        <v>3442.1</v>
+      </c>
+      <c r="D107">
+        <v>2509.7</v>
+      </c>
+      <c r="E107">
+        <v>2453.37</v>
+      </c>
+      <c r="F107" t="s">
+        <v>113</v>
+      </c>
+      <c r="G107" t="s">
+        <v>115</v>
+      </c>
+      <c r="H107" t="s">
+        <v>117</v>
+      </c>
+      <c r="I107" t="s">
+        <v>121</v>
+      </c>
+      <c r="J107" t="s">
+        <v>123</v>
+      </c>
+      <c r="K107">
+        <v>1838.35</v>
+      </c>
+      <c r="L107">
+        <v>1872.8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12">
+      <c r="A108" t="s">
+        <v>18</v>
+      </c>
+      <c r="B108">
+        <v>63.2</v>
+      </c>
+      <c r="C108">
+        <v>5902.9</v>
+      </c>
+      <c r="D108">
+        <v>2204.58</v>
+      </c>
+      <c r="E108">
+        <v>2097.93</v>
+      </c>
+      <c r="F108" t="s">
+        <v>113</v>
+      </c>
+      <c r="G108" t="s">
+        <v>116</v>
+      </c>
+      <c r="H108" t="s">
+        <v>117</v>
+      </c>
+      <c r="I108" t="s">
+        <v>121</v>
+      </c>
+      <c r="J108" t="s">
+        <v>124</v>
+      </c>
+      <c r="K108">
+        <v>1705.47</v>
+      </c>
+      <c r="L108">
+        <v>1651.82</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
+      <c r="A109" t="s">
+        <v>19</v>
+      </c>
+      <c r="B109">
+        <v>9854.700000000001</v>
+      </c>
+      <c r="C109">
+        <v>6836.8</v>
+      </c>
+      <c r="D109">
+        <v>2451.63</v>
+      </c>
+      <c r="E109">
+        <v>2407.18</v>
+      </c>
+      <c r="F109" t="s">
+        <v>113</v>
+      </c>
+      <c r="G109" t="s">
+        <v>115</v>
+      </c>
+      <c r="H109" t="s">
+        <v>117</v>
+      </c>
+      <c r="I109" t="s">
+        <v>121</v>
+      </c>
+      <c r="J109" t="s">
+        <v>124</v>
+      </c>
+      <c r="K109">
+        <v>1825.88</v>
+      </c>
+      <c r="L109">
+        <v>1792.01</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12">
+      <c r="A110" t="s">
+        <v>20</v>
+      </c>
+      <c r="B110">
+        <v>9564.799999999999</v>
+      </c>
+      <c r="C110">
+        <v>3554.1</v>
+      </c>
+      <c r="D110">
+        <v>2494.96</v>
+      </c>
+      <c r="E110">
+        <v>2440.88</v>
+      </c>
+      <c r="F110" t="s">
+        <v>113</v>
+      </c>
+      <c r="G110" t="s">
+        <v>115</v>
+      </c>
+      <c r="H110" t="s">
+        <v>119</v>
+      </c>
+      <c r="I110" t="s">
+        <v>121</v>
+      </c>
+      <c r="J110" t="s">
+        <v>124</v>
+      </c>
+      <c r="K110">
+        <v>1836.73</v>
+      </c>
+      <c r="L110">
+        <v>1859.58</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12">
+      <c r="A111" t="s">
+        <v>21</v>
+      </c>
+      <c r="B111">
+        <v>5615.2</v>
+      </c>
+      <c r="C111">
+        <v>5191</v>
+      </c>
+      <c r="D111">
+        <v>2337.51</v>
+      </c>
+      <c r="E111">
+        <v>2334.44</v>
+      </c>
+      <c r="F111" t="s">
+        <v>113</v>
+      </c>
+      <c r="G111" t="s">
+        <v>114</v>
+      </c>
+      <c r="H111" t="s">
+        <v>117</v>
+      </c>
+      <c r="I111" t="s">
+        <v>120</v>
+      </c>
+      <c r="J111" t="s">
+        <v>120</v>
+      </c>
+      <c r="K111">
+        <v>1753.88</v>
+      </c>
+      <c r="L111">
+        <v>1713.29</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12">
+      <c r="A112" t="s">
+        <v>22</v>
+      </c>
+      <c r="B112">
+        <v>3636.4</v>
+      </c>
+      <c r="C112">
+        <v>7652.5</v>
+      </c>
+      <c r="D112">
+        <v>2244.89</v>
+      </c>
+      <c r="E112">
+        <v>2146.39</v>
+      </c>
+      <c r="F112" t="s">
+        <v>113</v>
+      </c>
+      <c r="G112" t="s">
+        <v>116</v>
+      </c>
+      <c r="H112" t="s">
+        <v>117</v>
+      </c>
+      <c r="I112" t="s">
+        <v>121</v>
+      </c>
+      <c r="J112" t="s">
+        <v>124</v>
+      </c>
+      <c r="K112">
+        <v>1660.74</v>
+      </c>
+      <c r="L112">
+        <v>1598.76</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12">
+      <c r="A113" t="s">
+        <v>23</v>
+      </c>
+      <c r="B113">
+        <v>3341.1</v>
+      </c>
+      <c r="C113">
+        <v>9091.799999999999</v>
+      </c>
+      <c r="D113">
+        <v>2284.18</v>
+      </c>
+      <c r="E113">
+        <v>2226.14</v>
+      </c>
+      <c r="F113" t="s">
+        <v>113</v>
+      </c>
+      <c r="G113" t="s">
+        <v>116</v>
+      </c>
+      <c r="H113" t="s">
+        <v>117</v>
+      </c>
+      <c r="I113" t="s">
+        <v>121</v>
+      </c>
+      <c r="J113" t="s">
+        <v>122</v>
+      </c>
+      <c r="K113">
+        <v>1732.51</v>
+      </c>
+      <c r="L113">
+        <v>1706.4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12">
+      <c r="A114" t="s">
+        <v>24</v>
+      </c>
+      <c r="B114">
+        <v>3058.4</v>
+      </c>
+      <c r="C114">
+        <v>1510.6</v>
+      </c>
+      <c r="D114">
+        <v>2382.1</v>
+      </c>
+      <c r="E114">
+        <v>2476.22</v>
+      </c>
+      <c r="F114" t="s">
+        <v>113</v>
+      </c>
+      <c r="G114" t="s">
+        <v>116</v>
+      </c>
+      <c r="H114" t="s">
+        <v>117</v>
+      </c>
+      <c r="I114" t="s">
+        <v>121</v>
+      </c>
+      <c r="J114" t="s">
+        <v>124</v>
+      </c>
+      <c r="K114">
+        <v>1717.57</v>
+      </c>
+      <c r="L114">
+        <v>1784.12</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12">
+      <c r="A115" t="s">
+        <v>25</v>
+      </c>
+      <c r="B115">
+        <v>5340.9</v>
+      </c>
+      <c r="C115">
+        <v>9334.200000000001</v>
+      </c>
+      <c r="D115">
+        <v>2391.45</v>
+      </c>
+      <c r="E115">
+        <v>2361.53</v>
+      </c>
+      <c r="F115" t="s">
+        <v>112</v>
+      </c>
+      <c r="G115" t="s">
+        <v>114</v>
+      </c>
+      <c r="H115" t="s">
+        <v>117</v>
+      </c>
+      <c r="I115" t="s">
+        <v>121</v>
+      </c>
+      <c r="J115" t="s">
+        <v>123</v>
+      </c>
+      <c r="K115">
+        <v>1778.24</v>
+      </c>
+      <c r="L115">
+        <v>1753.27</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12">
+      <c r="A116" t="s">
+        <v>26</v>
+      </c>
+      <c r="B116">
+        <v>6054.6</v>
+      </c>
+      <c r="C116">
+        <v>51.8</v>
+      </c>
+      <c r="D116">
+        <v>2400.85</v>
+      </c>
+      <c r="E116">
+        <v>2401.28</v>
+      </c>
+      <c r="F116" t="s">
+        <v>113</v>
+      </c>
+      <c r="G116" t="s">
+        <v>114</v>
+      </c>
+      <c r="H116" t="s">
+        <v>117</v>
+      </c>
+      <c r="I116" t="s">
+        <v>121</v>
+      </c>
+      <c r="J116" t="s">
+        <v>122</v>
+      </c>
+      <c r="K116">
+        <v>1751.53</v>
+      </c>
+      <c r="L116">
+        <v>1797.8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12">
+      <c r="A117" t="s">
+        <v>27</v>
+      </c>
+      <c r="B117">
+        <v>6642</v>
+      </c>
+      <c r="C117">
+        <v>7529.8</v>
+      </c>
+      <c r="D117">
+        <v>2413.85</v>
+      </c>
+      <c r="E117">
+        <v>2345.47</v>
+      </c>
+      <c r="F117" t="s">
+        <v>112</v>
+      </c>
+      <c r="G117" t="s">
+        <v>114</v>
+      </c>
+      <c r="H117" t="s">
+        <v>119</v>
+      </c>
+      <c r="I117" t="s">
+        <v>120</v>
+      </c>
+      <c r="J117" t="s">
+        <v>120</v>
+      </c>
+      <c r="K117">
+        <v>1748.67</v>
+      </c>
+      <c r="L117">
+        <v>1842.75</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12">
+      <c r="A118" t="s">
+        <v>28</v>
+      </c>
+      <c r="B118">
+        <v>11946</v>
+      </c>
+      <c r="C118">
+        <v>8105.3</v>
+      </c>
+      <c r="D118">
+        <v>2502.95</v>
+      </c>
+      <c r="E118">
+        <v>2433.96</v>
+      </c>
+      <c r="F118" t="s">
+        <v>112</v>
+      </c>
+      <c r="G118" t="s">
+        <v>115</v>
+      </c>
+      <c r="H118" t="s">
+        <v>117</v>
+      </c>
+      <c r="I118" t="s">
+        <v>120</v>
+      </c>
+      <c r="J118" t="s">
+        <v>120</v>
+      </c>
+      <c r="K118">
+        <v>1835.14</v>
+      </c>
+      <c r="L118">
+        <v>1788.35</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12">
+      <c r="A119" t="s">
+        <v>29</v>
+      </c>
+      <c r="B119">
+        <v>9511.9</v>
+      </c>
+      <c r="C119">
+        <v>1367.6</v>
+      </c>
+      <c r="D119">
+        <v>2465.22</v>
+      </c>
+      <c r="E119">
+        <v>2421.73</v>
+      </c>
+      <c r="F119" t="s">
+        <v>113</v>
+      </c>
+      <c r="G119" t="s">
+        <v>115</v>
+      </c>
+      <c r="H119" t="s">
+        <v>118</v>
+      </c>
+      <c r="I119" t="s">
+        <v>121</v>
+      </c>
+      <c r="J119" t="s">
+        <v>123</v>
+      </c>
+      <c r="K119">
+        <v>1846.61</v>
+      </c>
+      <c r="L119">
+        <v>1778.5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12">
+      <c r="A120" t="s">
+        <v>30</v>
+      </c>
+      <c r="B120">
+        <v>7466.2</v>
+      </c>
+      <c r="C120">
+        <v>4189</v>
+      </c>
+      <c r="D120">
+        <v>2544.15</v>
+      </c>
+      <c r="E120">
+        <v>2600.01</v>
+      </c>
+      <c r="F120" t="s">
+        <v>112</v>
+      </c>
+      <c r="G120" t="s">
+        <v>114</v>
+      </c>
+      <c r="H120" t="s">
+        <v>117</v>
+      </c>
+      <c r="I120" t="s">
+        <v>121</v>
+      </c>
+      <c r="J120" t="s">
+        <v>124</v>
+      </c>
+      <c r="K120">
+        <v>1856.25</v>
+      </c>
+      <c r="L120">
+        <v>1885.66</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12">
+      <c r="A121" t="s">
+        <v>31</v>
+      </c>
+      <c r="B121">
+        <v>11867.5</v>
+      </c>
+      <c r="C121">
+        <v>8152.6</v>
+      </c>
+      <c r="D121">
+        <v>2455.33</v>
+      </c>
+      <c r="E121">
+        <v>2421.52</v>
+      </c>
+      <c r="F121" t="s">
+        <v>113</v>
+      </c>
+      <c r="G121" t="s">
+        <v>115</v>
+      </c>
+      <c r="H121" t="s">
+        <v>117</v>
+      </c>
+      <c r="I121" t="s">
+        <v>121</v>
+      </c>
+      <c r="J121" t="s">
+        <v>122</v>
+      </c>
+      <c r="K121">
+        <v>1768.97</v>
+      </c>
+      <c r="L121">
+        <v>1800.61</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12">
+      <c r="A122" t="s">
+        <v>32</v>
+      </c>
+      <c r="B122">
+        <v>2583.7</v>
+      </c>
+      <c r="C122">
+        <v>142.7</v>
+      </c>
+      <c r="D122">
+        <v>2410.15</v>
+      </c>
+      <c r="E122">
+        <v>2399.55</v>
+      </c>
+      <c r="F122" t="s">
+        <v>113</v>
+      </c>
+      <c r="G122" t="s">
+        <v>116</v>
+      </c>
+      <c r="H122" t="s">
+        <v>117</v>
+      </c>
+      <c r="I122" t="s">
+        <v>121</v>
+      </c>
+      <c r="J122" t="s">
+        <v>122</v>
+      </c>
+      <c r="K122">
+        <v>1770.9</v>
+      </c>
+      <c r="L122">
+        <v>1827.96</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12">
+      <c r="A123" t="s">
+        <v>33</v>
+      </c>
+      <c r="B123">
+        <v>1922.5</v>
+      </c>
+      <c r="C123">
+        <v>6284.6</v>
+      </c>
+      <c r="D123">
+        <v>2203.06</v>
+      </c>
+      <c r="E123">
+        <v>2121.46</v>
+      </c>
+      <c r="F123" t="s">
+        <v>113</v>
+      </c>
+      <c r="G123" t="s">
+        <v>116</v>
+      </c>
+      <c r="H123" t="s">
+        <v>117</v>
+      </c>
+      <c r="I123" t="s">
+        <v>121</v>
+      </c>
+      <c r="J123" t="s">
+        <v>122</v>
+      </c>
+      <c r="K123">
+        <v>1683.94</v>
+      </c>
+      <c r="L123">
+        <v>1648.33</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12">
+      <c r="A124" t="s">
+        <v>34</v>
+      </c>
+      <c r="B124">
+        <v>7350.5</v>
+      </c>
+      <c r="C124">
+        <v>7930.2</v>
+      </c>
+      <c r="D124">
+        <v>2320.26</v>
+      </c>
+      <c r="E124">
+        <v>2373.45</v>
+      </c>
+      <c r="F124" t="s">
+        <v>113</v>
+      </c>
+      <c r="G124" t="s">
+        <v>114</v>
+      </c>
+      <c r="H124" t="s">
+        <v>117</v>
+      </c>
+      <c r="I124" t="s">
+        <v>121</v>
+      </c>
+      <c r="J124" t="s">
+        <v>124</v>
+      </c>
+      <c r="K124">
+        <v>1731.69</v>
+      </c>
+      <c r="L124">
+        <v>1791.15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12">
+      <c r="A125" t="s">
+        <v>35</v>
+      </c>
+      <c r="B125">
+        <v>527.3</v>
+      </c>
+      <c r="C125">
+        <v>5130</v>
+      </c>
+      <c r="D125">
+        <v>2218.24</v>
+      </c>
+      <c r="E125">
+        <v>2177.5</v>
+      </c>
+      <c r="F125" t="s">
+        <v>113</v>
+      </c>
+      <c r="G125" t="s">
+        <v>116</v>
+      </c>
+      <c r="H125" t="s">
+        <v>117</v>
+      </c>
+      <c r="I125" t="s">
+        <v>121</v>
+      </c>
+      <c r="J125" t="s">
+        <v>124</v>
+      </c>
+      <c r="K125">
+        <v>1670.69</v>
+      </c>
+      <c r="L125">
+        <v>1596.3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12">
+      <c r="A126" t="s">
+        <v>36</v>
+      </c>
+      <c r="B126">
+        <v>428.2</v>
+      </c>
+      <c r="C126">
+        <v>7258.5</v>
+      </c>
+      <c r="D126">
+        <v>2200.46</v>
+      </c>
+      <c r="E126">
+        <v>2105.66</v>
+      </c>
+      <c r="F126" t="s">
+        <v>113</v>
+      </c>
+      <c r="G126" t="s">
+        <v>116</v>
+      </c>
+      <c r="H126" t="s">
+        <v>117</v>
+      </c>
+      <c r="I126" t="s">
+        <v>121</v>
+      </c>
+      <c r="J126" t="s">
+        <v>122</v>
+      </c>
+      <c r="K126">
+        <v>1625.77</v>
+      </c>
+      <c r="L126">
+        <v>1599.69</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12">
+      <c r="A127" t="s">
+        <v>37</v>
+      </c>
+      <c r="B127">
+        <v>6178.7</v>
+      </c>
+      <c r="C127">
+        <v>2264.2</v>
+      </c>
+      <c r="D127">
+        <v>2367.27</v>
+      </c>
+      <c r="E127">
+        <v>2425.59</v>
+      </c>
+      <c r="F127" t="s">
+        <v>113</v>
+      </c>
+      <c r="G127" t="s">
+        <v>114</v>
+      </c>
+      <c r="H127" t="s">
+        <v>119</v>
+      </c>
+      <c r="I127" t="s">
+        <v>121</v>
+      </c>
+      <c r="J127" t="s">
+        <v>124</v>
+      </c>
+      <c r="K127">
+        <v>1759.63</v>
+      </c>
+      <c r="L127">
+        <v>1792.51</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12">
+      <c r="A128" t="s">
+        <v>38</v>
+      </c>
+      <c r="B128">
+        <v>5594.5</v>
+      </c>
+      <c r="C128">
+        <v>1985.2</v>
+      </c>
+      <c r="D128">
+        <v>2376.88</v>
+      </c>
+      <c r="E128">
+        <v>2383.13</v>
+      </c>
+      <c r="F128" t="s">
+        <v>113</v>
+      </c>
+      <c r="G128" t="s">
+        <v>114</v>
+      </c>
+      <c r="H128" t="s">
+        <v>117</v>
+      </c>
+      <c r="I128" t="s">
+        <v>121</v>
+      </c>
+      <c r="J128" t="s">
+        <v>124</v>
+      </c>
+      <c r="K128">
+        <v>1764.3</v>
+      </c>
+      <c r="L128">
+        <v>1741.62</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12">
+      <c r="A129" t="s">
+        <v>39</v>
+      </c>
+      <c r="B129">
+        <v>11006</v>
+      </c>
+      <c r="C129">
+        <v>3631.3</v>
+      </c>
+      <c r="D129">
+        <v>2508.37</v>
+      </c>
+      <c r="E129">
+        <v>2453.16</v>
+      </c>
+      <c r="F129" t="s">
+        <v>113</v>
+      </c>
+      <c r="G129" t="s">
+        <v>115</v>
+      </c>
+      <c r="H129" t="s">
+        <v>118</v>
+      </c>
+      <c r="I129" t="s">
+        <v>121</v>
+      </c>
+      <c r="J129" t="s">
+        <v>123</v>
+      </c>
+      <c r="K129">
+        <v>1863.82</v>
+      </c>
+      <c r="L129">
+        <v>1786.3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12">
+      <c r="A130" t="s">
+        <v>40</v>
+      </c>
+      <c r="B130">
+        <v>7550.7</v>
+      </c>
+      <c r="C130">
+        <v>1794.1</v>
+      </c>
+      <c r="D130">
+        <v>2536.38</v>
+      </c>
+      <c r="E130">
+        <v>2531.87</v>
+      </c>
+      <c r="F130" t="s">
+        <v>112</v>
+      </c>
+      <c r="G130" t="s">
+        <v>114</v>
+      </c>
+      <c r="H130" t="s">
+        <v>119</v>
+      </c>
+      <c r="I130" t="s">
+        <v>121</v>
+      </c>
+      <c r="J130" t="s">
+        <v>122</v>
+      </c>
+      <c r="K130">
+        <v>1904.96</v>
+      </c>
+      <c r="L130">
+        <v>1862.72</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12">
+      <c r="A131" t="s">
+        <v>41</v>
+      </c>
+      <c r="B131">
+        <v>6169.4</v>
+      </c>
+      <c r="C131">
+        <v>3460.6</v>
+      </c>
+      <c r="D131">
+        <v>2370.05</v>
+      </c>
+      <c r="E131">
+        <v>2369.46</v>
+      </c>
+      <c r="F131" t="s">
+        <v>113</v>
+      </c>
+      <c r="G131" t="s">
+        <v>114</v>
+      </c>
+      <c r="H131" t="s">
+        <v>117</v>
+      </c>
+      <c r="I131" t="s">
+        <v>121</v>
+      </c>
+      <c r="J131" t="s">
+        <v>122</v>
+      </c>
+      <c r="K131">
+        <v>1767.37</v>
+      </c>
+      <c r="L131">
+        <v>1768.63</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12">
+      <c r="A132" t="s">
+        <v>42</v>
+      </c>
+      <c r="B132">
+        <v>5962.5</v>
+      </c>
+      <c r="C132">
+        <v>9481.200000000001</v>
+      </c>
+      <c r="D132">
+        <v>2256.26</v>
+      </c>
+      <c r="E132">
+        <v>2333.9</v>
+      </c>
+      <c r="F132" t="s">
+        <v>113</v>
+      </c>
+      <c r="G132" t="s">
+        <v>114</v>
+      </c>
+      <c r="H132" t="s">
+        <v>117</v>
+      </c>
+      <c r="I132" t="s">
+        <v>121</v>
+      </c>
+      <c r="J132" t="s">
+        <v>124</v>
+      </c>
+      <c r="K132">
+        <v>1645.53</v>
+      </c>
+      <c r="L132">
+        <v>1680.8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12">
+      <c r="A133" t="s">
+        <v>43</v>
+      </c>
+      <c r="B133">
+        <v>2970.2</v>
+      </c>
+      <c r="C133">
+        <v>5733.3</v>
+      </c>
+      <c r="D133">
+        <v>2313.96</v>
+      </c>
+      <c r="E133">
+        <v>2316.73</v>
+      </c>
+      <c r="F133" t="s">
+        <v>112</v>
+      </c>
+      <c r="G133" t="s">
+        <v>116</v>
+      </c>
+      <c r="H133" t="s">
+        <v>117</v>
+      </c>
+      <c r="I133" t="s">
+        <v>120</v>
+      </c>
+      <c r="J133" t="s">
+        <v>120</v>
+      </c>
+      <c r="K133">
+        <v>1702.56</v>
+      </c>
+      <c r="L133">
+        <v>1718.85</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12">
+      <c r="A134" t="s">
+        <v>44</v>
+      </c>
+      <c r="B134">
+        <v>141.5</v>
+      </c>
+      <c r="C134">
+        <v>3400.7</v>
+      </c>
+      <c r="D134">
+        <v>2254.68</v>
+      </c>
+      <c r="E134">
+        <v>2181.85</v>
+      </c>
+      <c r="F134" t="s">
+        <v>113</v>
+      </c>
+      <c r="G134" t="s">
+        <v>116</v>
+      </c>
+      <c r="H134" t="s">
+        <v>119</v>
+      </c>
+      <c r="I134" t="s">
+        <v>121</v>
+      </c>
+      <c r="J134" t="s">
+        <v>122</v>
+      </c>
+      <c r="K134">
+        <v>1663.53</v>
+      </c>
+      <c r="L134">
+        <v>1713.64</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12">
+      <c r="A135" t="s">
+        <v>45</v>
+      </c>
+      <c r="B135">
+        <v>2308.8</v>
+      </c>
+      <c r="C135">
+        <v>2715.2</v>
+      </c>
+      <c r="D135">
+        <v>2401.07</v>
+      </c>
+      <c r="E135">
+        <v>2344.52</v>
+      </c>
+      <c r="F135" t="s">
+        <v>112</v>
+      </c>
+      <c r="G135" t="s">
+        <v>116</v>
+      </c>
+      <c r="H135" t="s">
+        <v>117</v>
+      </c>
+      <c r="I135" t="s">
+        <v>121</v>
+      </c>
+      <c r="J135" t="s">
+        <v>124</v>
+      </c>
+      <c r="K135">
+        <v>1797.24</v>
+      </c>
+      <c r="L135">
+        <v>1704.61</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12">
+      <c r="A136" t="s">
+        <v>46</v>
+      </c>
+      <c r="B136">
+        <v>8304.4</v>
+      </c>
+      <c r="C136">
+        <v>9520.4</v>
+      </c>
+      <c r="D136">
+        <v>2365.63</v>
+      </c>
+      <c r="E136">
+        <v>2374.91</v>
+      </c>
+      <c r="F136" t="s">
+        <v>112</v>
+      </c>
+      <c r="G136" t="s">
+        <v>115</v>
+      </c>
+      <c r="H136" t="s">
+        <v>117</v>
+      </c>
+      <c r="I136" t="s">
+        <v>121</v>
+      </c>
+      <c r="J136" t="s">
+        <v>123</v>
+      </c>
+      <c r="K136">
+        <v>1747.32</v>
+      </c>
+      <c r="L136">
+        <v>1698.52</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12">
+      <c r="A137" t="s">
+        <v>47</v>
+      </c>
+      <c r="B137">
+        <v>2407.3</v>
+      </c>
+      <c r="C137">
+        <v>4444.8</v>
+      </c>
+      <c r="D137">
+        <v>2244.16</v>
+      </c>
+      <c r="E137">
+        <v>2208.07</v>
+      </c>
+      <c r="F137" t="s">
+        <v>113</v>
+      </c>
+      <c r="G137" t="s">
+        <v>116</v>
+      </c>
+      <c r="H137" t="s">
+        <v>119</v>
+      </c>
+      <c r="I137" t="s">
+        <v>121</v>
+      </c>
+      <c r="J137" t="s">
+        <v>122</v>
+      </c>
+      <c r="K137">
+        <v>1720.4</v>
+      </c>
+      <c r="L137">
+        <v>1681.35</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12">
+      <c r="A138" t="s">
+        <v>48</v>
+      </c>
+      <c r="B138">
+        <v>4434.4</v>
+      </c>
+      <c r="C138">
+        <v>9803.9</v>
+      </c>
+      <c r="D138">
+        <v>2266.92</v>
+      </c>
+      <c r="E138">
+        <v>2306.83</v>
+      </c>
+      <c r="F138" t="s">
+        <v>113</v>
+      </c>
+      <c r="G138" t="s">
+        <v>114</v>
+      </c>
+      <c r="H138" t="s">
+        <v>119</v>
+      </c>
+      <c r="I138" t="s">
+        <v>120</v>
+      </c>
+      <c r="J138" t="s">
+        <v>120</v>
+      </c>
+      <c r="K138">
+        <v>1700.61</v>
+      </c>
+      <c r="L138">
+        <v>1667.08</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12">
+      <c r="A139" t="s">
+        <v>49</v>
+      </c>
+      <c r="B139">
+        <v>44.8</v>
+      </c>
+      <c r="C139">
+        <v>5155.2</v>
+      </c>
+      <c r="D139">
+        <v>2231.93</v>
+      </c>
+      <c r="E139">
+        <v>2175.51</v>
+      </c>
+      <c r="F139" t="s">
+        <v>113</v>
+      </c>
+      <c r="G139" t="s">
+        <v>116</v>
+      </c>
+      <c r="H139" t="s">
+        <v>117</v>
+      </c>
+      <c r="I139" t="s">
+        <v>121</v>
+      </c>
+      <c r="J139" t="s">
+        <v>124</v>
+      </c>
+      <c r="K139">
+        <v>1686.86</v>
+      </c>
+      <c r="L139">
+        <v>1694.77</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12">
+      <c r="A140" t="s">
+        <v>50</v>
+      </c>
+      <c r="B140">
+        <v>9960.6</v>
+      </c>
+      <c r="C140">
+        <v>5211.7</v>
+      </c>
+      <c r="D140">
+        <v>2467.26</v>
+      </c>
+      <c r="E140">
+        <v>2426.25</v>
+      </c>
+      <c r="F140" t="s">
+        <v>113</v>
+      </c>
+      <c r="G140" t="s">
+        <v>115</v>
+      </c>
+      <c r="H140" t="s">
+        <v>119</v>
+      </c>
+      <c r="I140" t="s">
+        <v>120</v>
+      </c>
+      <c r="J140" t="s">
+        <v>120</v>
+      </c>
+      <c r="K140">
+        <v>1823.61</v>
+      </c>
+      <c r="L140">
+        <v>1890.94</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12">
+      <c r="A141" t="s">
+        <v>51</v>
+      </c>
+      <c r="B141">
+        <v>1853.5</v>
+      </c>
+      <c r="C141">
+        <v>8965.4</v>
+      </c>
+      <c r="D141">
+        <v>2337.03</v>
+      </c>
+      <c r="E141">
+        <v>2204.82</v>
+      </c>
+      <c r="F141" t="s">
+        <v>112</v>
+      </c>
+      <c r="G141" t="s">
+        <v>116</v>
+      </c>
+      <c r="H141" t="s">
+        <v>117</v>
+      </c>
+      <c r="I141" t="s">
+        <v>121</v>
+      </c>
+      <c r="J141" t="s">
+        <v>124</v>
+      </c>
+      <c r="K141">
+        <v>1763.7</v>
+      </c>
+      <c r="L141">
+        <v>1710.92</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12">
+      <c r="A142" t="s">
+        <v>52</v>
+      </c>
+      <c r="B142">
+        <v>3211.2</v>
+      </c>
+      <c r="C142">
+        <v>7427.7</v>
+      </c>
+      <c r="D142">
+        <v>2327.94</v>
+      </c>
+      <c r="E142">
+        <v>2244.27</v>
+      </c>
+      <c r="F142" t="s">
+        <v>112</v>
+      </c>
+      <c r="G142" t="s">
+        <v>116</v>
+      </c>
+      <c r="H142" t="s">
+        <v>117</v>
+      </c>
+      <c r="I142" t="s">
+        <v>121</v>
+      </c>
+      <c r="J142" t="s">
+        <v>124</v>
+      </c>
+      <c r="K142">
+        <v>1707.66</v>
+      </c>
+      <c r="L142">
+        <v>1697.51</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12">
+      <c r="A143" t="s">
+        <v>53</v>
+      </c>
+      <c r="B143">
+        <v>10564</v>
+      </c>
+      <c r="C143">
+        <v>5806.5</v>
+      </c>
+      <c r="D143">
+        <v>2469.62</v>
+      </c>
+      <c r="E143">
+        <v>2423.83</v>
+      </c>
+      <c r="F143" t="s">
+        <v>113</v>
+      </c>
+      <c r="G143" t="s">
+        <v>115</v>
+      </c>
+      <c r="H143" t="s">
+        <v>117</v>
+      </c>
+      <c r="I143" t="s">
+        <v>121</v>
+      </c>
+      <c r="J143" t="s">
+        <v>122</v>
+      </c>
+      <c r="K143">
+        <v>1871.25</v>
+      </c>
+      <c r="L143">
+        <v>1780.93</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12">
+      <c r="A144" t="s">
+        <v>54</v>
+      </c>
+      <c r="B144">
+        <v>6117.5</v>
+      </c>
+      <c r="C144">
+        <v>4266.5</v>
+      </c>
+      <c r="D144">
+        <v>2460.74</v>
+      </c>
+      <c r="E144">
+        <v>2468.55</v>
+      </c>
+      <c r="F144" t="s">
+        <v>112</v>
+      </c>
+      <c r="G144" t="s">
+        <v>114</v>
+      </c>
+      <c r="H144" t="s">
+        <v>117</v>
+      </c>
+      <c r="I144" t="s">
+        <v>120</v>
+      </c>
+      <c r="J144" t="s">
+        <v>120</v>
+      </c>
+      <c r="K144">
+        <v>1859.16</v>
+      </c>
+      <c r="L144">
+        <v>1825.23</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12">
+      <c r="A145" t="s">
+        <v>55</v>
+      </c>
+      <c r="B145">
+        <v>10165.8</v>
+      </c>
+      <c r="C145">
+        <v>8781.9</v>
+      </c>
+      <c r="D145">
+        <v>2356.91</v>
+      </c>
+      <c r="E145">
+        <v>2381.29</v>
+      </c>
+      <c r="F145" t="s">
+        <v>113</v>
+      </c>
+      <c r="G145" t="s">
+        <v>115</v>
+      </c>
+      <c r="H145" t="s">
+        <v>119</v>
+      </c>
+      <c r="I145" t="s">
+        <v>121</v>
+      </c>
+      <c r="J145" t="s">
+        <v>123</v>
+      </c>
+      <c r="K145">
+        <v>1784.86</v>
+      </c>
+      <c r="L145">
+        <v>1733.44</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12">
+      <c r="A146" t="s">
+        <v>56</v>
+      </c>
+      <c r="B146">
+        <v>7676.6</v>
+      </c>
+      <c r="C146">
+        <v>4116.5</v>
+      </c>
+      <c r="D146">
+        <v>2434.36</v>
+      </c>
+      <c r="E146">
+        <v>2478.3</v>
+      </c>
+      <c r="F146" t="s">
+        <v>113</v>
+      </c>
+      <c r="G146" t="s">
+        <v>114</v>
+      </c>
+      <c r="H146" t="s">
+        <v>117</v>
+      </c>
+      <c r="I146" t="s">
+        <v>121</v>
+      </c>
+      <c r="J146" t="s">
+        <v>122</v>
+      </c>
+      <c r="K146">
+        <v>1762.98</v>
+      </c>
+      <c r="L146">
+        <v>1772.76</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12">
+      <c r="A147" t="s">
+        <v>57</v>
+      </c>
+      <c r="B147">
+        <v>8901.299999999999</v>
+      </c>
+      <c r="C147">
+        <v>9227.6</v>
+      </c>
+      <c r="D147">
+        <v>2386.12</v>
+      </c>
+      <c r="E147">
+        <v>2393.05</v>
+      </c>
+      <c r="F147" t="s">
+        <v>112</v>
+      </c>
+      <c r="G147" t="s">
+        <v>115</v>
+      </c>
+      <c r="H147" t="s">
+        <v>117</v>
+      </c>
+      <c r="I147" t="s">
+        <v>121</v>
+      </c>
+      <c r="J147" t="s">
+        <v>122</v>
+      </c>
+      <c r="K147">
+        <v>1727.88</v>
+      </c>
+      <c r="L147">
+        <v>1813.48</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12">
+      <c r="A148" t="s">
+        <v>58</v>
+      </c>
+      <c r="B148">
+        <v>1097.9</v>
+      </c>
+      <c r="C148">
+        <v>687.2</v>
+      </c>
+      <c r="D148">
+        <v>2345.77</v>
+      </c>
+      <c r="E148">
+        <v>2234.23</v>
+      </c>
+      <c r="F148" t="s">
+        <v>113</v>
+      </c>
+      <c r="G148" t="s">
+        <v>116</v>
+      </c>
+      <c r="H148" t="s">
+        <v>117</v>
+      </c>
+      <c r="I148" t="s">
+        <v>121</v>
+      </c>
+      <c r="J148" t="s">
+        <v>123</v>
+      </c>
+      <c r="K148">
+        <v>1699.92</v>
+      </c>
+      <c r="L148">
+        <v>1662.94</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12">
+      <c r="A149" t="s">
+        <v>59</v>
+      </c>
+      <c r="B149">
+        <v>6493.7</v>
+      </c>
+      <c r="C149">
+        <v>4300</v>
+      </c>
+      <c r="D149">
+        <v>2379.37</v>
+      </c>
+      <c r="E149">
+        <v>2375.81</v>
+      </c>
+      <c r="F149" t="s">
+        <v>113</v>
+      </c>
+      <c r="G149" t="s">
+        <v>114</v>
+      </c>
+      <c r="H149" t="s">
+        <v>119</v>
+      </c>
+      <c r="I149" t="s">
+        <v>121</v>
+      </c>
+      <c r="J149" t="s">
+        <v>122</v>
+      </c>
+      <c r="K149">
+        <v>1726.18</v>
+      </c>
+      <c r="L149">
+        <v>1769.15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12">
+      <c r="A150" t="s">
+        <v>60</v>
+      </c>
+      <c r="B150">
+        <v>6093.3</v>
+      </c>
+      <c r="C150">
+        <v>5195.1</v>
+      </c>
+      <c r="D150">
+        <v>2366.94</v>
+      </c>
+      <c r="E150">
+        <v>2385.66</v>
+      </c>
+      <c r="F150" t="s">
+        <v>113</v>
+      </c>
+      <c r="G150" t="s">
+        <v>114</v>
+      </c>
+      <c r="H150" t="s">
+        <v>117</v>
+      </c>
+      <c r="I150" t="s">
+        <v>121</v>
+      </c>
+      <c r="J150" t="s">
+        <v>124</v>
+      </c>
+      <c r="K150">
+        <v>1772.25</v>
+      </c>
+      <c r="L150">
+        <v>1754.46</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12">
+      <c r="A151" t="s">
+        <v>61</v>
+      </c>
+      <c r="B151">
+        <v>10456.1</v>
+      </c>
+      <c r="C151">
+        <v>9509.4</v>
+      </c>
+      <c r="D151">
+        <v>2376.51</v>
+      </c>
+      <c r="E151">
+        <v>2373.9</v>
+      </c>
+      <c r="F151" t="s">
+        <v>113</v>
+      </c>
+      <c r="G151" t="s">
+        <v>115</v>
+      </c>
+      <c r="H151" t="s">
+        <v>119</v>
+      </c>
+      <c r="I151" t="s">
+        <v>121</v>
+      </c>
+      <c r="J151" t="s">
+        <v>124</v>
+      </c>
+      <c r="K151">
+        <v>1783.85</v>
+      </c>
+      <c r="L151">
+        <v>1801.23</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12">
+      <c r="A152" t="s">
+        <v>62</v>
+      </c>
+      <c r="B152">
+        <v>4335.2</v>
+      </c>
+      <c r="C152">
+        <v>2510</v>
+      </c>
+      <c r="D152">
+        <v>2433.5</v>
+      </c>
+      <c r="E152">
+        <v>2381.25</v>
+      </c>
+      <c r="F152" t="s">
+        <v>112</v>
+      </c>
+      <c r="G152" t="s">
+        <v>114</v>
+      </c>
+      <c r="H152" t="s">
+        <v>119</v>
+      </c>
+      <c r="I152" t="s">
+        <v>120</v>
+      </c>
+      <c r="J152" t="s">
+        <v>120</v>
+      </c>
+      <c r="K152">
+        <v>1845.06</v>
+      </c>
+      <c r="L152">
+        <v>1793.69</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12">
+      <c r="A153" t="s">
+        <v>63</v>
+      </c>
+      <c r="B153">
+        <v>7178.2</v>
+      </c>
+      <c r="C153">
+        <v>8060.4</v>
+      </c>
+      <c r="D153">
+        <v>2292.05</v>
+      </c>
+      <c r="E153">
+        <v>2323.82</v>
+      </c>
+      <c r="F153" t="s">
+        <v>113</v>
+      </c>
+      <c r="G153" t="s">
+        <v>114</v>
+      </c>
+      <c r="H153" t="s">
+        <v>118</v>
+      </c>
+      <c r="I153" t="s">
+        <v>120</v>
+      </c>
+      <c r="J153" t="s">
+        <v>120</v>
+      </c>
+      <c r="K153">
+        <v>1761.97</v>
+      </c>
+      <c r="L153">
+        <v>1734.25</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12">
+      <c r="A154" t="s">
+        <v>64</v>
+      </c>
+      <c r="B154">
+        <v>711</v>
+      </c>
+      <c r="C154">
+        <v>6764.7</v>
+      </c>
+      <c r="D154">
+        <v>2178.71</v>
+      </c>
+      <c r="E154">
+        <v>2062.44</v>
+      </c>
+      <c r="F154" t="s">
+        <v>113</v>
+      </c>
+      <c r="G154" t="s">
+        <v>116</v>
+      </c>
+      <c r="H154" t="s">
+        <v>117</v>
+      </c>
+      <c r="I154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J154" t="s">
+        <v>122</v>
+      </c>
+      <c r="K154">
+        <v>1660.33</v>
+      </c>
+      <c r="L154">
+        <v>1561.99</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12">
+      <c r="A155" t="s">
+        <v>65</v>
+      </c>
+      <c r="B155">
+        <v>4651.6</v>
+      </c>
+      <c r="C155">
+        <v>7170.9</v>
+      </c>
+      <c r="D155">
+        <v>2256.98</v>
+      </c>
+      <c r="E155">
+        <v>2305.02</v>
+      </c>
+      <c r="F155" t="s">
+        <v>113</v>
+      </c>
+      <c r="G155" t="s">
+        <v>114</v>
+      </c>
+      <c r="H155" t="s">
+        <v>117</v>
+      </c>
+      <c r="I155" t="s">
+        <v>121</v>
+      </c>
+      <c r="J155" t="s">
+        <v>122</v>
+      </c>
+      <c r="K155">
+        <v>1699.95</v>
+      </c>
+      <c r="L155">
+        <v>1700.16</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12">
+      <c r="A156" t="s">
+        <v>66</v>
+      </c>
+      <c r="B156">
+        <v>3876.4</v>
+      </c>
+      <c r="C156">
+        <v>6296.2</v>
+      </c>
+      <c r="D156">
+        <v>2337.76</v>
+      </c>
+      <c r="E156">
+        <v>2231.29</v>
+      </c>
+      <c r="F156" t="s">
+        <v>112</v>
+      </c>
+      <c r="G156" t="s">
+        <v>116</v>
+      </c>
+      <c r="H156" t="s">
+        <v>117</v>
+      </c>
+      <c r="I156" t="s">
+        <v>121</v>
+      </c>
+      <c r="J156" t="s">
+        <v>124</v>
+      </c>
+      <c r="K156">
+        <v>1743.24</v>
+      </c>
+      <c r="L156">
+        <v>1746.34</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12">
+      <c r="A157" t="s">
+        <v>67</v>
+      </c>
+      <c r="B157">
+        <v>1802.4</v>
+      </c>
+      <c r="C157">
+        <v>9715.6</v>
+      </c>
+      <c r="D157">
+        <v>2247.32</v>
+      </c>
+      <c r="E157">
+        <v>2130.65</v>
+      </c>
+      <c r="F157" t="s">
+        <v>113</v>
+      </c>
+      <c r="G157" t="s">
+        <v>116</v>
+      </c>
+      <c r="H157" t="s">
+        <v>117</v>
+      </c>
+      <c r="I157" t="s">
+        <v>121</v>
+      </c>
+      <c r="J157" t="s">
+        <v>123</v>
+      </c>
+      <c r="K157">
+        <v>1678.44</v>
+      </c>
+      <c r="L157">
+        <v>1695.64</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12">
+      <c r="A158" t="s">
+        <v>68</v>
+      </c>
+      <c r="B158">
+        <v>9796.1</v>
+      </c>
+      <c r="C158">
+        <v>3326.8</v>
+      </c>
+      <c r="D158">
+        <v>2492.69</v>
+      </c>
+      <c r="E158">
+        <v>2439.41</v>
+      </c>
+      <c r="F158" t="s">
+        <v>113</v>
+      </c>
+      <c r="G158" t="s">
+        <v>115</v>
+      </c>
+      <c r="H158" t="s">
+        <v>117</v>
+      </c>
+      <c r="I158" t="s">
+        <v>121</v>
+      </c>
+      <c r="J158" t="s">
+        <v>123</v>
+      </c>
+      <c r="K158">
+        <v>1787.71</v>
+      </c>
+      <c r="L158">
+        <v>1798.98</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12">
+      <c r="A159" t="s">
+        <v>69</v>
+      </c>
+      <c r="B159">
+        <v>4553.4</v>
+      </c>
+      <c r="C159">
+        <v>3982.8</v>
+      </c>
+      <c r="D159">
+        <v>2304.55</v>
+      </c>
+      <c r="E159">
+        <v>2336.69</v>
+      </c>
+      <c r="F159" t="s">
+        <v>113</v>
+      </c>
+      <c r="G159" t="s">
+        <v>114</v>
+      </c>
+      <c r="H159" t="s">
+        <v>117</v>
+      </c>
+      <c r="I159" t="s">
+        <v>121</v>
+      </c>
+      <c r="J159" t="s">
+        <v>122</v>
+      </c>
+      <c r="K159">
+        <v>1730.45</v>
+      </c>
+      <c r="L159">
+        <v>1776.58</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12">
+      <c r="A160" t="s">
+        <v>70</v>
+      </c>
+      <c r="B160">
+        <v>11745</v>
+      </c>
+      <c r="C160">
+        <v>2029.1</v>
+      </c>
+      <c r="D160">
+        <v>2521.45</v>
+      </c>
+      <c r="E160">
+        <v>2470.46</v>
+      </c>
+      <c r="F160" t="s">
+        <v>113</v>
+      </c>
+      <c r="G160" t="s">
+        <v>115</v>
+      </c>
+      <c r="H160" t="s">
+        <v>119</v>
+      </c>
+      <c r="I160" t="s">
+        <v>120</v>
+      </c>
+      <c r="J160" t="s">
+        <v>120</v>
+      </c>
+      <c r="K160">
+        <v>1838.95</v>
+      </c>
+      <c r="L160">
+        <v>1900.65</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12">
+      <c r="A161" t="s">
+        <v>71</v>
+      </c>
+      <c r="B161">
+        <v>7079.9</v>
+      </c>
+      <c r="C161">
+        <v>507</v>
+      </c>
+      <c r="D161">
+        <v>2390.74</v>
+      </c>
+      <c r="E161">
+        <v>2404.62</v>
+      </c>
+      <c r="F161" t="s">
+        <v>113</v>
+      </c>
+      <c r="G161" t="s">
+        <v>114</v>
+      </c>
+      <c r="H161" t="s">
+        <v>118</v>
+      </c>
+      <c r="I161" t="s">
+        <v>120</v>
+      </c>
+      <c r="J161" t="s">
+        <v>120</v>
+      </c>
+      <c r="K161">
+        <v>1746.56</v>
+      </c>
+      <c r="L161">
+        <v>1746.38</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12">
+      <c r="A162" t="s">
+        <v>72</v>
+      </c>
+      <c r="B162">
+        <v>7260.7</v>
+      </c>
+      <c r="C162">
+        <v>2129.1</v>
+      </c>
+      <c r="D162">
+        <v>2411.95</v>
+      </c>
+      <c r="E162">
+        <v>2402.67</v>
+      </c>
+      <c r="F162" t="s">
+        <v>113</v>
+      </c>
+      <c r="G162" t="s">
+        <v>114</v>
+      </c>
+      <c r="H162" t="s">
+        <v>117</v>
+      </c>
+      <c r="I162" t="s">
+        <v>121</v>
+      </c>
+      <c r="J162" t="s">
+        <v>123</v>
+      </c>
+      <c r="K162">
+        <v>1751.78</v>
+      </c>
+      <c r="L162">
+        <v>1684.19</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12">
+      <c r="A163" t="s">
+        <v>73</v>
+      </c>
+      <c r="B163">
+        <v>7656</v>
+      </c>
+      <c r="C163">
+        <v>9154.6</v>
+      </c>
+      <c r="D163">
+        <v>2273.61</v>
+      </c>
+      <c r="E163">
+        <v>2262.61</v>
+      </c>
+      <c r="F163" t="s">
+        <v>113</v>
+      </c>
+      <c r="G163" t="s">
+        <v>114</v>
+      </c>
+      <c r="H163" t="s">
+        <v>117</v>
+      </c>
+      <c r="I163" t="s">
+        <v>120</v>
+      </c>
+      <c r="J163" t="s">
+        <v>120</v>
+      </c>
+      <c r="K163">
+        <v>1710.51</v>
+      </c>
+      <c r="L163">
+        <v>1658.82</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12">
+      <c r="A164" t="s">
+        <v>74</v>
+      </c>
+      <c r="B164">
+        <v>8117.4</v>
+      </c>
+      <c r="C164">
+        <v>8401.700000000001</v>
+      </c>
+      <c r="D164">
+        <v>2313.64</v>
+      </c>
+      <c r="E164">
+        <v>2332.12</v>
+      </c>
+      <c r="F164" t="s">
+        <v>113</v>
+      </c>
+      <c r="G164" t="s">
+        <v>114</v>
+      </c>
+      <c r="H164" t="s">
+        <v>117</v>
+      </c>
+      <c r="I164" t="s">
+        <v>121</v>
+      </c>
+      <c r="J164" t="s">
+        <v>124</v>
+      </c>
+      <c r="K164">
+        <v>1755.42</v>
+      </c>
+      <c r="L164">
+        <v>1716.84</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12">
+      <c r="A165" t="s">
+        <v>75</v>
+      </c>
+      <c r="B165">
+        <v>1809.5</v>
+      </c>
+      <c r="C165">
+        <v>1124.1</v>
+      </c>
+      <c r="D165">
+        <v>2439.21</v>
+      </c>
+      <c r="E165">
+        <v>2374.08</v>
+      </c>
+      <c r="F165" t="s">
+        <v>112</v>
+      </c>
+      <c r="G165" t="s">
+        <v>116</v>
+      </c>
+      <c r="H165" t="s">
+        <v>117</v>
+      </c>
+      <c r="I165" t="s">
+        <v>121</v>
+      </c>
+      <c r="J165" t="s">
+        <v>124</v>
+      </c>
+      <c r="K165">
+        <v>1807.85</v>
+      </c>
+      <c r="L165">
+        <v>1808.98</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12">
+      <c r="A166" t="s">
+        <v>76</v>
+      </c>
+      <c r="B166">
+        <v>5283.8</v>
+      </c>
+      <c r="C166">
+        <v>6037.8</v>
+      </c>
+      <c r="D166">
+        <v>2317.02</v>
+      </c>
+      <c r="E166">
+        <v>2277.78</v>
+      </c>
+      <c r="F166" t="s">
+        <v>113</v>
+      </c>
+      <c r="G166" t="s">
+        <v>114</v>
+      </c>
+      <c r="H166" t="s">
+        <v>117</v>
+      </c>
+      <c r="I166" t="s">
+        <v>121</v>
+      </c>
+      <c r="J166" t="s">
+        <v>123</v>
+      </c>
+      <c r="K166">
+        <v>1731.09</v>
+      </c>
+      <c r="L166">
+        <v>1701.69</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12">
+      <c r="A167" t="s">
+        <v>77</v>
+      </c>
+      <c r="B167">
+        <v>2874.8</v>
+      </c>
+      <c r="C167">
+        <v>4792</v>
+      </c>
+      <c r="D167">
+        <v>2323.36</v>
+      </c>
+      <c r="E167">
+        <v>2228.45</v>
+      </c>
+      <c r="F167" t="s">
+        <v>112</v>
+      </c>
+      <c r="G167" t="s">
+        <v>116</v>
+      </c>
+      <c r="H167" t="s">
+        <v>117</v>
+      </c>
+      <c r="I167" t="s">
+        <v>121</v>
+      </c>
+      <c r="J167" t="s">
+        <v>122</v>
+      </c>
+      <c r="K167">
+        <v>1730.03</v>
+      </c>
+      <c r="L167">
+        <v>1690.01</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12">
+      <c r="A168" t="s">
+        <v>78</v>
+      </c>
+      <c r="B168">
+        <v>4830</v>
+      </c>
+      <c r="C168">
+        <v>5946.8</v>
+      </c>
+      <c r="D168">
+        <v>2280.17</v>
+      </c>
+      <c r="E168">
+        <v>2269.8</v>
+      </c>
+      <c r="F168" t="s">
+        <v>113</v>
+      </c>
+      <c r="G168" t="s">
+        <v>114</v>
+      </c>
+      <c r="H168" t="s">
+        <v>117</v>
+      </c>
+      <c r="I168" t="s">
+        <v>120</v>
+      </c>
+      <c r="J168" t="s">
+        <v>120</v>
+      </c>
+      <c r="K168">
+        <v>1694.58</v>
+      </c>
+      <c r="L168">
+        <v>1723.38</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12">
+      <c r="A169" t="s">
+        <v>79</v>
+      </c>
+      <c r="B169">
+        <v>1160.4</v>
+      </c>
+      <c r="C169">
+        <v>6592.8</v>
+      </c>
+      <c r="D169">
+        <v>2205.41</v>
+      </c>
+      <c r="E169">
+        <v>2145.65</v>
+      </c>
+      <c r="F169" t="s">
+        <v>113</v>
+      </c>
+      <c r="G169" t="s">
+        <v>116</v>
+      </c>
+      <c r="H169" t="s">
+        <v>119</v>
+      </c>
+      <c r="I169" t="s">
+        <v>120</v>
+      </c>
+      <c r="J169" t="s">
+        <v>120</v>
+      </c>
+      <c r="K169">
+        <v>1656.4</v>
+      </c>
+      <c r="L169">
+        <v>1603.85</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12">
+      <c r="A170" t="s">
+        <v>80</v>
+      </c>
+      <c r="B170">
+        <v>11613.9</v>
+      </c>
+      <c r="C170">
+        <v>3066.6</v>
+      </c>
+      <c r="D170">
+        <v>2526.83</v>
+      </c>
+      <c r="E170">
+        <v>2466.69</v>
+      </c>
+      <c r="F170" t="s">
+        <v>113</v>
+      </c>
+      <c r="G170" t="s">
+        <v>115</v>
+      </c>
+      <c r="H170" t="s">
+        <v>118</v>
+      </c>
+      <c r="I170" t="s">
+        <v>121</v>
+      </c>
+      <c r="J170" t="s">
+        <v>122</v>
+      </c>
+      <c r="K170">
+        <v>1830.42</v>
+      </c>
+      <c r="L170">
+        <v>1749.58</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12">
+      <c r="A171" t="s">
+        <v>81</v>
+      </c>
+      <c r="B171">
+        <v>2580</v>
+      </c>
+      <c r="C171">
+        <v>9613.5</v>
+      </c>
+      <c r="D171">
+        <v>2251.16</v>
+      </c>
+      <c r="E171">
+        <v>2244.46</v>
+      </c>
+      <c r="F171" t="s">
+        <v>113</v>
+      </c>
+      <c r="G171" t="s">
+        <v>116</v>
+      </c>
+      <c r="H171" t="s">
+        <v>117</v>
+      </c>
+      <c r="I171" t="s">
+        <v>120</v>
+      </c>
+      <c r="J171" t="s">
+        <v>120</v>
+      </c>
+      <c r="K171">
+        <v>1672.12</v>
+      </c>
+      <c r="L171">
+        <v>1651.01</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12">
+      <c r="A172" t="s">
+        <v>82</v>
+      </c>
+      <c r="B172">
+        <v>8061.2</v>
+      </c>
+      <c r="C172">
+        <v>4658.4</v>
+      </c>
+      <c r="D172">
+        <v>2441.94</v>
+      </c>
+      <c r="E172">
+        <v>2453.46</v>
+      </c>
+      <c r="F172" t="s">
+        <v>113</v>
+      </c>
+      <c r="G172" t="s">
+        <v>114</v>
+      </c>
+      <c r="H172" t="s">
+        <v>119</v>
+      </c>
+      <c r="I172" t="s">
+        <v>121</v>
+      </c>
+      <c r="J172" t="s">
+        <v>123</v>
+      </c>
+      <c r="K172">
+        <v>1795.8</v>
+      </c>
+      <c r="L172">
+        <v>1849.28</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12">
+      <c r="A173" t="s">
+        <v>83</v>
+      </c>
+      <c r="B173">
+        <v>3605</v>
+      </c>
+      <c r="C173">
+        <v>6281</v>
+      </c>
+      <c r="D173">
+        <v>2248.84</v>
+      </c>
+      <c r="E173">
+        <v>2178.3</v>
+      </c>
+      <c r="F173" t="s">
+        <v>113</v>
+      </c>
+      <c r="G173" t="s">
+        <v>116</v>
+      </c>
+      <c r="H173" t="s">
+        <v>117</v>
+      </c>
+      <c r="I173" t="s">
+        <v>121</v>
+      </c>
+      <c r="J173" t="s">
+        <v>124</v>
+      </c>
+      <c r="K173">
+        <v>1723.68</v>
+      </c>
+      <c r="L173">
+        <v>1623.09</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12">
+      <c r="A174" t="s">
+        <v>84</v>
+      </c>
+      <c r="B174">
+        <v>10488.9</v>
+      </c>
+      <c r="C174">
+        <v>6352.3</v>
+      </c>
+      <c r="D174">
+        <v>2525.05</v>
+      </c>
+      <c r="E174">
+        <v>2454.02</v>
+      </c>
+      <c r="F174" t="s">
+        <v>112</v>
+      </c>
+      <c r="G174" t="s">
+        <v>115</v>
+      </c>
+      <c r="H174" t="s">
+        <v>117</v>
+      </c>
+      <c r="I174" t="s">
+        <v>121</v>
+      </c>
+      <c r="J174" t="s">
+        <v>124</v>
+      </c>
+      <c r="K174">
+        <v>1824.38</v>
+      </c>
+      <c r="L174">
+        <v>1843.93</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12">
+      <c r="A175" t="s">
+        <v>85</v>
+      </c>
+      <c r="B175">
+        <v>7946.6</v>
+      </c>
+      <c r="C175">
+        <v>1838.9</v>
+      </c>
+      <c r="D175">
+        <v>2393.62</v>
+      </c>
+      <c r="E175">
+        <v>2395.36</v>
+      </c>
+      <c r="F175" t="s">
+        <v>113</v>
+      </c>
+      <c r="G175" t="s">
+        <v>114</v>
+      </c>
+      <c r="H175" t="s">
+        <v>119</v>
+      </c>
+      <c r="I175" t="s">
+        <v>120</v>
+      </c>
+      <c r="J175" t="s">
+        <v>120</v>
+      </c>
+      <c r="K175">
+        <v>1794.44</v>
+      </c>
+      <c r="L175">
+        <v>1788.16</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12">
+      <c r="A176" t="s">
+        <v>86</v>
+      </c>
+      <c r="B176">
+        <v>1579.4</v>
+      </c>
+      <c r="C176">
+        <v>618.7</v>
+      </c>
+      <c r="D176">
+        <v>2372</v>
+      </c>
+      <c r="E176">
+        <v>2343.67</v>
+      </c>
+      <c r="F176" t="s">
+        <v>113</v>
+      </c>
+      <c r="G176" t="s">
+        <v>116</v>
+      </c>
+      <c r="H176" t="s">
+        <v>118</v>
+      </c>
+      <c r="I176" t="s">
+        <v>121</v>
+      </c>
+      <c r="J176" t="s">
+        <v>122</v>
+      </c>
+      <c r="K176">
+        <v>1745.79</v>
+      </c>
+      <c r="L176">
+        <v>1757.91</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12">
+      <c r="A177" t="s">
+        <v>87</v>
+      </c>
+      <c r="B177">
+        <v>10140.9</v>
+      </c>
+      <c r="C177">
+        <v>4115.2</v>
+      </c>
+      <c r="D177">
+        <v>2517.67</v>
+      </c>
+      <c r="E177">
+        <v>2456.29</v>
+      </c>
+      <c r="F177" t="s">
+        <v>113</v>
+      </c>
+      <c r="G177" t="s">
+        <v>115</v>
+      </c>
+      <c r="H177" t="s">
+        <v>119</v>
+      </c>
+      <c r="I177" t="s">
+        <v>121</v>
+      </c>
+      <c r="J177" t="s">
+        <v>122</v>
+      </c>
+      <c r="K177">
+        <v>1823.62</v>
+      </c>
+      <c r="L177">
+        <v>1833.98</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12">
+      <c r="A178" t="s">
+        <v>88</v>
+      </c>
+      <c r="B178">
+        <v>11339.4</v>
+      </c>
+      <c r="C178">
+        <v>7640.3</v>
+      </c>
+      <c r="D178">
+        <v>2436.34</v>
+      </c>
+      <c r="E178">
+        <v>2395.87</v>
+      </c>
+      <c r="F178" t="s">
+        <v>113</v>
+      </c>
+      <c r="G178" t="s">
+        <v>115</v>
+      </c>
+      <c r="H178" t="s">
+        <v>119</v>
+      </c>
+      <c r="I178" t="s">
+        <v>121</v>
+      </c>
+      <c r="J178" t="s">
+        <v>124</v>
+      </c>
+      <c r="K178">
+        <v>1729.88</v>
+      </c>
+      <c r="L178">
+        <v>1716.61</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12">
+      <c r="A179" t="s">
+        <v>89</v>
+      </c>
+      <c r="B179">
+        <v>10847</v>
+      </c>
+      <c r="C179">
+        <v>8152.2</v>
+      </c>
+      <c r="D179">
+        <v>2402.62</v>
+      </c>
+      <c r="E179">
+        <v>2394.75</v>
+      </c>
+      <c r="F179" t="s">
+        <v>113</v>
+      </c>
+      <c r="G179" t="s">
+        <v>115</v>
+      </c>
+      <c r="H179" t="s">
+        <v>117</v>
+      </c>
+      <c r="I179" t="s">
+        <v>120</v>
+      </c>
+      <c r="J179" t="s">
+        <v>120</v>
+      </c>
+      <c r="K179">
+        <v>1705.94</v>
+      </c>
+      <c r="L179">
+        <v>1752.39</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12">
+      <c r="A180" t="s">
+        <v>90</v>
+      </c>
+      <c r="B180">
+        <v>6836.6</v>
+      </c>
+      <c r="C180">
+        <v>7299.9</v>
+      </c>
+      <c r="D180">
+        <v>2351.31</v>
+      </c>
+      <c r="E180">
+        <v>2333</v>
+      </c>
+      <c r="F180" t="s">
+        <v>113</v>
+      </c>
+      <c r="G180" t="s">
+        <v>114</v>
+      </c>
+      <c r="H180" t="s">
+        <v>117</v>
+      </c>
+      <c r="I180" t="s">
+        <v>120</v>
+      </c>
+      <c r="J180" t="s">
+        <v>120</v>
+      </c>
+      <c r="K180">
+        <v>1762.76</v>
+      </c>
+      <c r="L180">
+        <v>1797.21</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12">
+      <c r="A181" t="s">
+        <v>91</v>
+      </c>
+      <c r="B181">
+        <v>1745.5</v>
+      </c>
+      <c r="C181">
+        <v>1132</v>
+      </c>
+      <c r="D181">
+        <v>2351.51</v>
+      </c>
+      <c r="E181">
+        <v>2406.18</v>
+      </c>
+      <c r="F181" t="s">
+        <v>113</v>
+      </c>
+      <c r="G181" t="s">
+        <v>116</v>
+      </c>
+      <c r="H181" t="s">
+        <v>117</v>
+      </c>
+      <c r="I181" t="s">
+        <v>120</v>
+      </c>
+      <c r="J181" t="s">
+        <v>120</v>
+      </c>
+      <c r="K181">
+        <v>1712.12</v>
+      </c>
+      <c r="L181">
+        <v>1741.83</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12">
+      <c r="A182" t="s">
+        <v>92</v>
+      </c>
+      <c r="B182">
+        <v>2309.6</v>
+      </c>
+      <c r="C182">
+        <v>9133.5</v>
+      </c>
+      <c r="D182">
+        <v>2230.47</v>
+      </c>
+      <c r="E182">
+        <v>2199.01</v>
+      </c>
+      <c r="F182" t="s">
+        <v>113</v>
+      </c>
+      <c r="G182" t="s">
+        <v>116</v>
+      </c>
+      <c r="H182" t="s">
+        <v>117</v>
+      </c>
+      <c r="I182" t="s">
+        <v>120</v>
+      </c>
+      <c r="J182" t="s">
+        <v>120</v>
+      </c>
+      <c r="K182">
+        <v>1697.46</v>
+      </c>
+      <c r="L182">
+        <v>1599.52</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12">
+      <c r="A183" t="s">
+        <v>93</v>
+      </c>
+      <c r="B183">
+        <v>11134.9</v>
+      </c>
+      <c r="C183">
+        <v>8020.4</v>
+      </c>
+      <c r="D183">
+        <v>2423.52</v>
+      </c>
+      <c r="E183">
+        <v>2391.84</v>
+      </c>
+      <c r="F183" t="s">
+        <v>113</v>
+      </c>
+      <c r="G183" t="s">
+        <v>115</v>
+      </c>
+      <c r="H183" t="s">
+        <v>117</v>
+      </c>
+      <c r="I183" t="s">
+        <v>120</v>
+      </c>
+      <c r="J183" t="s">
+        <v>120</v>
+      </c>
+      <c r="K183">
+        <v>1782.85</v>
+      </c>
+      <c r="L183">
+        <v>1801.66</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12">
+      <c r="A184" t="s">
+        <v>94</v>
+      </c>
+      <c r="B184">
+        <v>6627.9</v>
+      </c>
+      <c r="C184">
+        <v>8776.9</v>
+      </c>
+      <c r="D184">
+        <v>2383.1</v>
+      </c>
+      <c r="E184">
+        <v>2357.58</v>
+      </c>
+      <c r="F184" t="s">
+        <v>112</v>
+      </c>
+      <c r="G184" t="s">
+        <v>114</v>
+      </c>
+      <c r="H184" t="s">
+        <v>117</v>
+      </c>
+      <c r="I184" t="s">
+        <v>121</v>
+      </c>
+      <c r="J184" t="s">
+        <v>124</v>
+      </c>
+      <c r="K184">
+        <v>1786.21</v>
+      </c>
+      <c r="L184">
+        <v>1715.7</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12">
+      <c r="A185" t="s">
+        <v>95</v>
+      </c>
+      <c r="B185">
+        <v>2166.6</v>
+      </c>
+      <c r="C185">
+        <v>5233</v>
+      </c>
+      <c r="D185">
+        <v>2207.11</v>
+      </c>
+      <c r="E185">
+        <v>2027.08</v>
+      </c>
+      <c r="F185" t="s">
+        <v>113</v>
+      </c>
+      <c r="G185" t="s">
+        <v>116</v>
+      </c>
+      <c r="H185" t="s">
+        <v>119</v>
+      </c>
+      <c r="I185" t="s">
+        <v>121</v>
+      </c>
+      <c r="J185" t="s">
+        <v>123</v>
+      </c>
+      <c r="K185">
+        <v>1697.07</v>
+      </c>
+      <c r="L185">
+        <v>1682.11</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12">
+      <c r="A186" t="s">
+        <v>96</v>
+      </c>
+      <c r="B186">
+        <v>10608.7</v>
+      </c>
+      <c r="C186">
+        <v>9156.4</v>
+      </c>
+      <c r="D186">
+        <v>2369.8</v>
+      </c>
+      <c r="E186">
+        <v>2383.25</v>
+      </c>
+      <c r="F186" t="s">
+        <v>113</v>
+      </c>
+      <c r="G186" t="s">
+        <v>115</v>
+      </c>
+      <c r="H186" t="s">
+        <v>118</v>
+      </c>
+      <c r="I186" t="s">
+        <v>120</v>
+      </c>
+      <c r="J186" t="s">
+        <v>120</v>
+      </c>
+      <c r="K186">
+        <v>1751.49</v>
+      </c>
+      <c r="L186">
+        <v>1758.38</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12">
+      <c r="A187" t="s">
+        <v>97</v>
+      </c>
+      <c r="B187">
+        <v>7698.9</v>
+      </c>
+      <c r="C187">
+        <v>466.5</v>
+      </c>
+      <c r="D187">
+        <v>2407.85</v>
+      </c>
+      <c r="E187">
+        <v>2413.67</v>
+      </c>
+      <c r="F187" t="s">
+        <v>113</v>
+      </c>
+      <c r="G187" t="s">
+        <v>114</v>
+      </c>
+      <c r="H187" t="s">
+        <v>118</v>
+      </c>
+      <c r="I187" t="s">
+        <v>121</v>
+      </c>
+      <c r="J187" t="s">
+        <v>124</v>
+      </c>
+      <c r="K187">
+        <v>1685.18</v>
+      </c>
+      <c r="L187">
+        <v>1808.56</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12">
+      <c r="A188" t="s">
+        <v>98</v>
+      </c>
+      <c r="B188">
+        <v>6836.3</v>
+      </c>
+      <c r="C188">
+        <v>302.9</v>
+      </c>
+      <c r="D188">
+        <v>2412.72</v>
+      </c>
+      <c r="E188">
+        <v>2455.73</v>
+      </c>
+      <c r="F188" t="s">
+        <v>113</v>
+      </c>
+      <c r="G188" t="s">
+        <v>114</v>
+      </c>
+      <c r="H188" t="s">
+        <v>117</v>
+      </c>
+      <c r="I188" t="s">
+        <v>121</v>
+      </c>
+      <c r="J188" t="s">
+        <v>122</v>
+      </c>
+      <c r="K188">
+        <v>1728.95</v>
+      </c>
+      <c r="L188">
+        <v>1803.82</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12">
+      <c r="A189" t="s">
+        <v>99</v>
+      </c>
+      <c r="B189">
+        <v>4515.5</v>
+      </c>
+      <c r="C189">
+        <v>202.2</v>
+      </c>
+      <c r="D189">
+        <v>2529.32</v>
+      </c>
+      <c r="E189">
+        <v>2608.46</v>
+      </c>
+      <c r="F189" t="s">
+        <v>112</v>
+      </c>
+      <c r="G189" t="s">
+        <v>114</v>
+      </c>
+      <c r="H189" t="s">
+        <v>117</v>
+      </c>
+      <c r="I189" t="s">
+        <v>121</v>
+      </c>
+      <c r="J189" t="s">
+        <v>124</v>
+      </c>
+      <c r="K189">
+        <v>1881.51</v>
+      </c>
+      <c r="L189">
+        <v>1868.97</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12">
+      <c r="A190" t="s">
+        <v>100</v>
+      </c>
+      <c r="B190">
+        <v>4931.5</v>
+      </c>
+      <c r="C190">
+        <v>2527.7</v>
+      </c>
+      <c r="D190">
+        <v>2371.21</v>
+      </c>
+      <c r="E190">
+        <v>2352.09</v>
+      </c>
+      <c r="F190" t="s">
+        <v>113</v>
+      </c>
+      <c r="G190" t="s">
+        <v>114</v>
+      </c>
+      <c r="H190" t="s">
+        <v>119</v>
+      </c>
+      <c r="I190" t="s">
+        <v>120</v>
+      </c>
+      <c r="J190" t="s">
+        <v>120</v>
+      </c>
+      <c r="K190">
+        <v>1805.2</v>
+      </c>
+      <c r="L190">
+        <v>1791.87</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12">
+      <c r="A191" t="s">
+        <v>101</v>
+      </c>
+      <c r="B191">
+        <v>2873.9</v>
+      </c>
+      <c r="C191">
+        <v>2485.7</v>
+      </c>
+      <c r="D191">
+        <v>2321.94</v>
+      </c>
+      <c r="E191">
+        <v>2248.77</v>
+      </c>
+      <c r="F191" t="s">
+        <v>113</v>
+      </c>
+      <c r="G191" t="s">
+        <v>116</v>
+      </c>
+      <c r="H191" t="s">
+        <v>117</v>
+      </c>
+      <c r="I191" t="s">
+        <v>121</v>
+      </c>
+      <c r="J191" t="s">
+        <v>124</v>
+      </c>
+      <c r="K191">
+        <v>1723.08</v>
+      </c>
+      <c r="L191">
+        <v>1714.4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12">
+      <c r="A192" t="s">
+        <v>102</v>
+      </c>
+      <c r="B192">
+        <v>456.7</v>
+      </c>
+      <c r="C192">
+        <v>1875</v>
+      </c>
+      <c r="D192">
+        <v>2298.97</v>
+      </c>
+      <c r="E192">
+        <v>2280.21</v>
+      </c>
+      <c r="F192" t="s">
+        <v>113</v>
+      </c>
+      <c r="G192" t="s">
+        <v>116</v>
+      </c>
+      <c r="H192" t="s">
+        <v>119</v>
+      </c>
+      <c r="I192" t="s">
+        <v>120</v>
+      </c>
+      <c r="J192" t="s">
+        <v>120</v>
+      </c>
+      <c r="K192">
+        <v>1695.83</v>
+      </c>
+      <c r="L192">
+        <v>1668.74</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12">
+      <c r="A193" t="s">
+        <v>103</v>
+      </c>
+      <c r="B193">
+        <v>10514.6</v>
+      </c>
+      <c r="C193">
+        <v>5670.6</v>
+      </c>
+      <c r="D193">
+        <v>2480.25</v>
+      </c>
+      <c r="E193">
+        <v>2434.44</v>
+      </c>
+      <c r="F193" t="s">
+        <v>113</v>
+      </c>
+      <c r="G193" t="s">
+        <v>115</v>
+      </c>
+      <c r="H193" t="s">
+        <v>117</v>
+      </c>
+      <c r="I193" t="s">
+        <v>121</v>
+      </c>
+      <c r="J193" t="s">
+        <v>122</v>
+      </c>
+      <c r="K193">
+        <v>1777.4</v>
+      </c>
+      <c r="L193">
+        <v>1799.86</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12">
+      <c r="A194" t="s">
+        <v>104</v>
+      </c>
+      <c r="B194">
+        <v>5612.8</v>
+      </c>
+      <c r="C194">
+        <v>389.9</v>
+      </c>
+      <c r="D194">
+        <v>2400.92</v>
+      </c>
+      <c r="E194">
+        <v>2365.06</v>
+      </c>
+      <c r="F194" t="s">
+        <v>113</v>
+      </c>
+      <c r="G194" t="s">
+        <v>114</v>
+      </c>
+      <c r="H194" t="s">
+        <v>117</v>
+      </c>
+      <c r="I194" t="s">
+        <v>121</v>
+      </c>
+      <c r="J194" t="s">
+        <v>124</v>
+      </c>
+      <c r="K194">
+        <v>1779.4</v>
+      </c>
+      <c r="L194">
+        <v>1696.54</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12">
+      <c r="A195" t="s">
+        <v>105</v>
+      </c>
+      <c r="B195">
+        <v>6571.6</v>
+      </c>
+      <c r="C195">
+        <v>5903.9</v>
+      </c>
+      <c r="D195">
+        <v>2353.34</v>
+      </c>
+      <c r="E195">
+        <v>2385.89</v>
+      </c>
+      <c r="F195" t="s">
+        <v>113</v>
+      </c>
+      <c r="G195" t="s">
+        <v>114</v>
+      </c>
+      <c r="H195" t="s">
+        <v>117</v>
+      </c>
+      <c r="I195" t="s">
+        <v>120</v>
+      </c>
+      <c r="J195" t="s">
+        <v>120</v>
+      </c>
+      <c r="K195">
+        <v>1694.36</v>
+      </c>
+      <c r="L195">
+        <v>1740.17</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12">
+      <c r="A196" t="s">
+        <v>106</v>
+      </c>
+      <c r="B196">
+        <v>3866</v>
+      </c>
+      <c r="C196">
+        <v>1660.1</v>
+      </c>
+      <c r="D196">
+        <v>2385.9</v>
+      </c>
+      <c r="E196">
+        <v>2397.12</v>
+      </c>
+      <c r="F196" t="s">
+        <v>113</v>
+      </c>
+      <c r="G196" t="s">
+        <v>116</v>
+      </c>
+      <c r="H196" t="s">
+        <v>119</v>
+      </c>
+      <c r="I196" t="s">
+        <v>121</v>
+      </c>
+      <c r="J196" t="s">
+        <v>124</v>
+      </c>
+      <c r="K196">
+        <v>1726.14</v>
+      </c>
+      <c r="L196">
+        <v>1708.17</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12">
+      <c r="A197" t="s">
+        <v>107</v>
+      </c>
+      <c r="B197">
+        <v>9015.9</v>
+      </c>
+      <c r="C197">
+        <v>6778.7</v>
+      </c>
+      <c r="D197">
+        <v>2441.25</v>
+      </c>
+      <c r="E197">
+        <v>2409.69</v>
+      </c>
+      <c r="F197" t="s">
+        <v>113</v>
+      </c>
+      <c r="G197" t="s">
+        <v>115</v>
+      </c>
+      <c r="H197" t="s">
+        <v>117</v>
+      </c>
+      <c r="I197" t="s">
+        <v>121</v>
+      </c>
+      <c r="J197" t="s">
+        <v>124</v>
+      </c>
+      <c r="K197">
+        <v>1797.33</v>
+      </c>
+      <c r="L197">
+        <v>1774.82</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12">
+      <c r="A198" t="s">
+        <v>108</v>
+      </c>
+      <c r="B198">
+        <v>302.4</v>
+      </c>
+      <c r="C198">
+        <v>210.8</v>
+      </c>
+      <c r="D198">
+        <v>2307.42</v>
+      </c>
+      <c r="E198">
+        <v>2265.41</v>
+      </c>
+      <c r="F198" t="s">
+        <v>113</v>
+      </c>
+      <c r="G198" t="s">
+        <v>116</v>
+      </c>
+      <c r="H198" t="s">
+        <v>117</v>
+      </c>
+      <c r="I198" t="s">
+        <v>121</v>
+      </c>
+      <c r="J198" t="s">
+        <v>124</v>
+      </c>
+      <c r="K198">
+        <v>1718.62</v>
+      </c>
+      <c r="L198">
+        <v>1735.96</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12">
+      <c r="A199" t="s">
+        <v>109</v>
+      </c>
+      <c r="B199">
+        <v>4466.2</v>
+      </c>
+      <c r="C199">
+        <v>3105.7</v>
+      </c>
+      <c r="D199">
+        <v>2323.34</v>
+      </c>
+      <c r="E199">
+        <v>2322.42</v>
+      </c>
+      <c r="F199" t="s">
+        <v>113</v>
+      </c>
+      <c r="G199" t="s">
+        <v>114</v>
+      </c>
+      <c r="H199" t="s">
+        <v>118</v>
+      </c>
+      <c r="I199" t="s">
+        <v>120</v>
+      </c>
+      <c r="J199" t="s">
+        <v>120</v>
+      </c>
+      <c r="K199">
+        <v>1716.48</v>
+      </c>
+      <c r="L199">
+        <v>1746.38</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12">
+      <c r="A200" t="s">
+        <v>110</v>
+      </c>
+      <c r="B200">
+        <v>364.2</v>
+      </c>
+      <c r="C200">
+        <v>9383.4</v>
+      </c>
+      <c r="D200">
+        <v>2170.67</v>
+      </c>
+      <c r="E200">
+        <v>2011.14</v>
+      </c>
+      <c r="F200" t="s">
+        <v>113</v>
+      </c>
+      <c r="G200" t="s">
+        <v>116</v>
+      </c>
+      <c r="H200" t="s">
+        <v>118</v>
+      </c>
+      <c r="I200" t="s">
+        <v>121</v>
+      </c>
+      <c r="J200" t="s">
+        <v>124</v>
+      </c>
+      <c r="K200">
+        <v>1671.53</v>
+      </c>
+      <c r="L200">
+        <v>1585.88</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12">
+      <c r="A201" t="s">
+        <v>111</v>
+      </c>
+      <c r="B201">
+        <v>1474.7</v>
+      </c>
+      <c r="C201">
+        <v>5384</v>
+      </c>
+      <c r="D201">
+        <v>2212.74</v>
+      </c>
+      <c r="E201">
+        <v>2217.34</v>
+      </c>
+      <c r="F201" t="s">
+        <v>113</v>
+      </c>
+      <c r="G201" t="s">
+        <v>116</v>
+      </c>
+      <c r="H201" t="s">
+        <v>117</v>
+      </c>
+      <c r="I201" t="s">
+        <v>121</v>
+      </c>
+      <c r="J201" t="s">
+        <v>124</v>
+      </c>
+      <c r="K201">
+        <v>1634.69</v>
+      </c>
+      <c r="L201">
+        <v>1533.52</v>
       </c>
     </row>
   </sheetData>
